--- a/output/Tables/mmc1.xlsx
+++ b/output/Tables/mmc1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\luzh29\Library\Projects\WGS_GWAS_and_MR\output\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF663A3-BAF1-4542-A625-5C102654447A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CA66F7-520E-44BA-9BB8-0EFFD13D540A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="692" activeTab="1" xr2:uid="{B1B36BAE-942B-7148-AF58-4A36D0B24BEE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="490">
   <si>
     <t>Disease</t>
   </si>
@@ -1559,1989 +1559,127 @@
     <t>Participant ID</t>
   </si>
   <si>
-    <t>p31</t>
-  </si>
-  <si>
-    <t>Sex</t>
-  </si>
-  <si>
-    <t>p22001</t>
-  </si>
-  <si>
-    <t>Genetic sex</t>
-  </si>
-  <si>
-    <t>p21022</t>
-  </si>
-  <si>
-    <t>Age at recruitment</t>
-  </si>
-  <si>
-    <t>p21001_i0</t>
-  </si>
-  <si>
-    <t>Body mass index (BMI) | Instance 0</t>
-  </si>
-  <si>
-    <t>p21001_i1</t>
-  </si>
-  <si>
-    <t>Body mass index (BMI) | Instance 1</t>
-  </si>
-  <si>
-    <t>p21001_i2</t>
-  </si>
-  <si>
-    <t>Body mass index (BMI) | Instance 2</t>
-  </si>
-  <si>
-    <t>p21001_i3</t>
-  </si>
-  <si>
-    <t>Body mass index (BMI) | Instance 3</t>
-  </si>
-  <si>
-    <t>p21000_i0</t>
-  </si>
-  <si>
-    <t>Ethnic background | Instance 0</t>
-  </si>
-  <si>
-    <t>p21000_i1</t>
-  </si>
-  <si>
-    <t>Ethnic background | Instance 1</t>
-  </si>
-  <si>
-    <t>p21000_i2</t>
-  </si>
-  <si>
-    <t>Ethnic background | Instance 2</t>
-  </si>
-  <si>
-    <t>p21000_i3</t>
-  </si>
-  <si>
-    <t>Ethnic background | Instance 3</t>
-  </si>
-  <si>
-    <t>p22006</t>
-  </si>
-  <si>
-    <t>Genetic ethnic grouping</t>
-  </si>
-  <si>
-    <t>p22027</t>
-  </si>
-  <si>
-    <t>Outliers for heterozygosity or missing rate</t>
-  </si>
-  <si>
-    <t>p20116_i0</t>
-  </si>
-  <si>
-    <t>Smoking status | Instance 0</t>
-  </si>
-  <si>
-    <t>p20116_i1</t>
-  </si>
-  <si>
-    <t>Smoking status | Instance 1</t>
-  </si>
-  <si>
-    <t>p20116_i2</t>
-  </si>
-  <si>
-    <t>Smoking status | Instance 2</t>
-  </si>
-  <si>
-    <t>p20116_i3</t>
-  </si>
-  <si>
-    <t>Smoking status | Instance 3</t>
-  </si>
-  <si>
-    <t>p1558_i0</t>
-  </si>
-  <si>
-    <t>Alcohol intake frequency. | Instance 0</t>
-  </si>
-  <si>
-    <t>p1558_i1</t>
-  </si>
-  <si>
-    <t>Alcohol intake frequency. | Instance 1</t>
-  </si>
-  <si>
-    <t>p1558_i2</t>
-  </si>
-  <si>
-    <t>Alcohol intake frequency. | Instance 2</t>
-  </si>
-  <si>
-    <t>p1558_i3</t>
-  </si>
-  <si>
-    <t>Alcohol intake frequency. | Instance 3</t>
-  </si>
-  <si>
-    <t>p22189</t>
-  </si>
-  <si>
-    <t>Townsend deprivation index at recruitment</t>
-  </si>
-  <si>
-    <t>p22000</t>
-  </si>
-  <si>
-    <t>Genotype measurement batch</t>
-  </si>
-  <si>
-    <t>p22009_a1</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 1</t>
-  </si>
-  <si>
-    <t>p22009_a2</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 2</t>
-  </si>
-  <si>
-    <t>p22009_a3</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 3</t>
-  </si>
-  <si>
-    <t>p22009_a4</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 4</t>
-  </si>
-  <si>
-    <t>p22009_a5</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 5</t>
-  </si>
-  <si>
-    <t>p22009_a6</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 6</t>
-  </si>
-  <si>
-    <t>p22009_a7</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 7</t>
-  </si>
-  <si>
-    <t>p22009_a8</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 8</t>
-  </si>
-  <si>
-    <t>p22009_a9</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 9</t>
-  </si>
-  <si>
-    <t>p22009_a10</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 10</t>
-  </si>
-  <si>
-    <t>p22009_a11</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 11</t>
-  </si>
-  <si>
-    <t>p22009_a12</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 12</t>
-  </si>
-  <si>
-    <t>p22009_a13</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 13</t>
-  </si>
-  <si>
-    <t>p22009_a14</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 14</t>
-  </si>
-  <si>
-    <t>p22009_a15</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 15</t>
-  </si>
-  <si>
-    <t>p22009_a16</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 16</t>
-  </si>
-  <si>
-    <t>p22009_a17</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 17</t>
-  </si>
-  <si>
-    <t>p22009_a18</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 18</t>
-  </si>
-  <si>
-    <t>p22009_a19</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 19</t>
-  </si>
-  <si>
-    <t>p22009_a20</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 20</t>
-  </si>
-  <si>
-    <t>p22009_a21</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 21</t>
-  </si>
-  <si>
-    <t>p22009_a22</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 22</t>
-  </si>
-  <si>
-    <t>p22009_a23</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 23</t>
-  </si>
-  <si>
-    <t>p22009_a24</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 24</t>
-  </si>
-  <si>
-    <t>p22009_a25</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 25</t>
-  </si>
-  <si>
-    <t>p22009_a26</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 26</t>
-  </si>
-  <si>
-    <t>p22009_a27</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 27</t>
-  </si>
-  <si>
-    <t>p22009_a28</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 28</t>
-  </si>
-  <si>
-    <t>p22009_a29</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 29</t>
-  </si>
-  <si>
-    <t>p22009_a30</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 30</t>
-  </si>
-  <si>
-    <t>p22009_a31</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 31</t>
-  </si>
-  <si>
-    <t>p22009_a32</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 32</t>
-  </si>
-  <si>
-    <t>p22009_a33</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 33</t>
-  </si>
-  <si>
-    <t>p22009_a34</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 34</t>
-  </si>
-  <si>
-    <t>p22009_a35</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 35</t>
-  </si>
-  <si>
-    <t>p22009_a36</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 36</t>
-  </si>
-  <si>
-    <t>p22009_a37</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 37</t>
-  </si>
-  <si>
-    <t>p22009_a38</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 38</t>
-  </si>
-  <si>
-    <t>p22009_a39</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 39</t>
-  </si>
-  <si>
-    <t>p22009_a40</t>
-  </si>
-  <si>
-    <t>Genetic principal components | Array 40</t>
-  </si>
-  <si>
-    <t>p53_i0</t>
-  </si>
-  <si>
-    <t>Date of attending assessment centre | Instance 0</t>
-  </si>
-  <si>
-    <t>p53_i1</t>
-  </si>
-  <si>
-    <t>Date of attending assessment centre | Instance 1</t>
-  </si>
-  <si>
-    <t>p53_i2</t>
-  </si>
-  <si>
-    <t>Date of attending assessment centre | Instance 2</t>
-  </si>
-  <si>
-    <t>p53_i3</t>
-  </si>
-  <si>
-    <t>Date of attending assessment centre | Instance 3</t>
-  </si>
-  <si>
-    <t>p40000_i0</t>
-  </si>
-  <si>
-    <t>Date of death | Instance 0</t>
-  </si>
-  <si>
-    <t>p40000_i1</t>
-  </si>
-  <si>
-    <t>Date of death | Instance 1</t>
-  </si>
-  <si>
-    <t>p40005_i0</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 0</t>
-  </si>
-  <si>
-    <t>p40005_i1</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 1</t>
-  </si>
-  <si>
-    <t>p40005_i2</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 2</t>
-  </si>
-  <si>
-    <t>p40005_i3</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 3</t>
-  </si>
-  <si>
-    <t>p40005_i4</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 4</t>
-  </si>
-  <si>
-    <t>p40005_i5</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 5</t>
-  </si>
-  <si>
-    <t>p40005_i6</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 6</t>
-  </si>
-  <si>
-    <t>p40005_i7</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 7</t>
-  </si>
-  <si>
-    <t>p40005_i8</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 8</t>
-  </si>
-  <si>
-    <t>p40005_i9</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 9</t>
-  </si>
-  <si>
-    <t>p40005_i10</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 10</t>
-  </si>
-  <si>
-    <t>p40005_i11</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 11</t>
-  </si>
-  <si>
-    <t>p40005_i12</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 12</t>
-  </si>
-  <si>
-    <t>p40005_i13</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 13</t>
-  </si>
-  <si>
-    <t>p40005_i14</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 14</t>
-  </si>
-  <si>
-    <t>p40005_i15</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 15</t>
-  </si>
-  <si>
-    <t>p40005_i16</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 16</t>
-  </si>
-  <si>
-    <t>p40005_i17</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 17</t>
-  </si>
-  <si>
-    <t>p40005_i18</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 18</t>
-  </si>
-  <si>
-    <t>p40005_i19</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 19</t>
-  </si>
-  <si>
-    <t>p40005_i20</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 20</t>
-  </si>
-  <si>
-    <t>p40005_i21</t>
-  </si>
-  <si>
-    <t>Date of cancer diagnosis | Instance 21</t>
-  </si>
-  <si>
-    <t>p40006_i0</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 0</t>
-  </si>
-  <si>
-    <t>p40006_i1</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 1</t>
-  </si>
-  <si>
-    <t>p40006_i2</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 2</t>
-  </si>
-  <si>
-    <t>p40006_i3</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 3</t>
-  </si>
-  <si>
-    <t>p40006_i4</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 4</t>
-  </si>
-  <si>
-    <t>p40006_i5</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 5</t>
-  </si>
-  <si>
-    <t>p40006_i6</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 6</t>
-  </si>
-  <si>
-    <t>p40006_i7</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 7</t>
-  </si>
-  <si>
-    <t>p40006_i8</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 8</t>
-  </si>
-  <si>
-    <t>p40006_i9</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 9</t>
-  </si>
-  <si>
-    <t>p40006_i10</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 10</t>
-  </si>
-  <si>
-    <t>p40006_i11</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 11</t>
-  </si>
-  <si>
-    <t>p40006_i12</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 12</t>
-  </si>
-  <si>
-    <t>p40006_i13</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 13</t>
-  </si>
-  <si>
-    <t>p40006_i14</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 14</t>
-  </si>
-  <si>
-    <t>p40006_i15</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 15</t>
-  </si>
-  <si>
-    <t>p40006_i16</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 16</t>
-  </si>
-  <si>
-    <t>p40006_i17</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 17</t>
-  </si>
-  <si>
-    <t>p40006_i18</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 18</t>
-  </si>
-  <si>
-    <t>p40006_i19</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 19</t>
-  </si>
-  <si>
-    <t>p40006_i20</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 20</t>
-  </si>
-  <si>
-    <t>p40006_i21</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD10 | Instance 21</t>
-  </si>
-  <si>
-    <t>p40013_i0</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 0</t>
-  </si>
-  <si>
-    <t>p40013_i1</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 1</t>
-  </si>
-  <si>
-    <t>p40013_i2</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 2</t>
-  </si>
-  <si>
-    <t>p40013_i3</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 3</t>
-  </si>
-  <si>
-    <t>p40013_i4</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 4</t>
-  </si>
-  <si>
-    <t>p40013_i5</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 5</t>
-  </si>
-  <si>
-    <t>p40013_i6</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 6</t>
-  </si>
-  <si>
-    <t>p40013_i7</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 7</t>
-  </si>
-  <si>
-    <t>p40013_i8</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 8</t>
-  </si>
-  <si>
-    <t>p40013_i9</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 9</t>
-  </si>
-  <si>
-    <t>p40013_i10</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 10</t>
-  </si>
-  <si>
-    <t>p40013_i11</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 11</t>
-  </si>
-  <si>
-    <t>p40013_i12</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 12</t>
-  </si>
-  <si>
-    <t>p40013_i13</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 13</t>
-  </si>
-  <si>
-    <t>p40013_i14</t>
-  </si>
-  <si>
-    <t>Type of cancer: ICD9 | Instance 14</t>
-  </si>
-  <si>
-    <t>p20001_i0_a0</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 0 | Array 0</t>
-  </si>
-  <si>
-    <t>p20001_i0_a1</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 0 | Array 1</t>
-  </si>
-  <si>
-    <t>p20001_i0_a2</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 0 | Array 2</t>
-  </si>
-  <si>
-    <t>p20001_i0_a3</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 0 | Array 3</t>
-  </si>
-  <si>
-    <t>p20001_i0_a4</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 0 | Array 4</t>
-  </si>
-  <si>
-    <t>p20001_i0_a5</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 0 | Array 5</t>
-  </si>
-  <si>
-    <t>p20001_i1_a0</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 1 | Array 0</t>
-  </si>
-  <si>
-    <t>p20001_i1_a1</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 1 | Array 1</t>
-  </si>
-  <si>
-    <t>p20001_i1_a2</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 1 | Array 2</t>
-  </si>
-  <si>
-    <t>p20001_i1_a3</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 1 | Array 3</t>
-  </si>
-  <si>
-    <t>p20001_i1_a4</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 1 | Array 4</t>
-  </si>
-  <si>
-    <t>p20001_i1_a5</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 1 | Array 5</t>
-  </si>
-  <si>
-    <t>p20001_i2_a0</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 2 | Array 0</t>
-  </si>
-  <si>
-    <t>p20001_i2_a1</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 2 | Array 1</t>
-  </si>
-  <si>
-    <t>p20001_i2_a2</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 2 | Array 2</t>
-  </si>
-  <si>
-    <t>p20001_i2_a3</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 2 | Array 3</t>
-  </si>
-  <si>
-    <t>p20001_i2_a4</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 2 | Array 4</t>
-  </si>
-  <si>
-    <t>p20001_i2_a5</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 2 | Array 5</t>
-  </si>
-  <si>
-    <t>p20001_i3_a0</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 3 | Array 0</t>
-  </si>
-  <si>
-    <t>p20001_i3_a1</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 3 | Array 1</t>
-  </si>
-  <si>
-    <t>p20001_i3_a2</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 3 | Array 2</t>
-  </si>
-  <si>
-    <t>p20001_i3_a3</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 3 | Array 3</t>
-  </si>
-  <si>
-    <t>p20001_i3_a4</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 3 | Array 4</t>
-  </si>
-  <si>
-    <t>p20001_i3_a5</t>
-  </si>
-  <si>
-    <t>Cancer code, self-reported | Instance 3 | Array 5</t>
-  </si>
-  <si>
-    <t>p40001_i0</t>
-  </si>
-  <si>
-    <t>Underlying (primary) cause of death: ICD10 | Instance 0</t>
-  </si>
-  <si>
-    <t>p40001_i1</t>
-  </si>
-  <si>
-    <t>Underlying (primary) cause of death: ICD10 | Instance 1</t>
-  </si>
-  <si>
-    <t>p40002_i0_a0</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 0</t>
-  </si>
-  <si>
-    <t>p40002_i0_a1</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 1</t>
-  </si>
-  <si>
-    <t>p40002_i0_a2</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 2</t>
-  </si>
-  <si>
-    <t>p40002_i0_a3</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 3</t>
-  </si>
-  <si>
-    <t>p40002_i0_a4</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 4</t>
-  </si>
-  <si>
-    <t>p40002_i0_a5</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 5</t>
-  </si>
-  <si>
-    <t>p40002_i0_a6</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 6</t>
-  </si>
-  <si>
-    <t>p40002_i0_a7</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 7</t>
-  </si>
-  <si>
-    <t>p40002_i0_a8</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 8</t>
-  </si>
-  <si>
-    <t>p40002_i0_a9</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 9</t>
-  </si>
-  <si>
-    <t>p40002_i0_a10</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 10</t>
-  </si>
-  <si>
-    <t>p40002_i0_a11</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 11</t>
-  </si>
-  <si>
-    <t>p40002_i0_a12</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 12</t>
-  </si>
-  <si>
-    <t>p40002_i0_a13</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 13</t>
-  </si>
-  <si>
-    <t>p40002_i0_a14</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 0 | Array 14</t>
-  </si>
-  <si>
-    <t>p40002_i1_a0</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 0</t>
-  </si>
-  <si>
-    <t>p40002_i1_a1</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 1</t>
-  </si>
-  <si>
-    <t>p40002_i1_a2</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 2</t>
-  </si>
-  <si>
-    <t>p40002_i1_a3</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 3</t>
-  </si>
-  <si>
-    <t>p40002_i1_a4</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 4</t>
-  </si>
-  <si>
-    <t>p40002_i1_a5</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 5</t>
-  </si>
-  <si>
-    <t>p40002_i1_a6</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 6</t>
-  </si>
-  <si>
-    <t>p40002_i1_a7</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 7</t>
-  </si>
-  <si>
-    <t>p40002_i1_a8</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 8</t>
-  </si>
-  <si>
-    <t>p40002_i1_a9</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 9</t>
-  </si>
-  <si>
-    <t>p40002_i1_a10</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 10</t>
-  </si>
-  <si>
-    <t>p40002_i1_a11</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 11</t>
-  </si>
-  <si>
-    <t>p40002_i1_a12</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 12</t>
-  </si>
-  <si>
-    <t>p40002_i1_a13</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 13</t>
-  </si>
-  <si>
-    <t>p40002_i1_a14</t>
-  </si>
-  <si>
-    <t>Contributory (secondary) causes of death: ICD10 | Instance 1 | Array 14</t>
-  </si>
-  <si>
-    <t>p41202</t>
-  </si>
-  <si>
-    <t>Diagnoses - main ICD10</t>
-  </si>
-  <si>
-    <t>p41203</t>
-  </si>
-  <si>
-    <t>Diagnoses - main ICD9</t>
-  </si>
-  <si>
-    <t>p41204</t>
-  </si>
-  <si>
-    <t>Diagnoses - secondary ICD10</t>
-  </si>
-  <si>
-    <t>p41205</t>
-  </si>
-  <si>
-    <t>Diagnoses - secondary ICD9</t>
-  </si>
-  <si>
-    <t>p20002_i0_a0</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 0</t>
-  </si>
-  <si>
-    <t>p20002_i0_a1</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 1</t>
-  </si>
-  <si>
-    <t>p20002_i0_a2</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 2</t>
-  </si>
-  <si>
-    <t>p20002_i0_a3</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 3</t>
-  </si>
-  <si>
-    <t>p20002_i0_a4</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 4</t>
-  </si>
-  <si>
-    <t>p20002_i0_a5</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 5</t>
-  </si>
-  <si>
-    <t>p20002_i0_a6</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 6</t>
-  </si>
-  <si>
-    <t>p20002_i0_a7</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 7</t>
-  </si>
-  <si>
-    <t>p20002_i0_a8</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 8</t>
-  </si>
-  <si>
-    <t>p20002_i0_a9</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 9</t>
-  </si>
-  <si>
-    <t>p20002_i0_a10</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 10</t>
-  </si>
-  <si>
-    <t>p20002_i0_a11</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 11</t>
-  </si>
-  <si>
-    <t>p20002_i0_a12</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 12</t>
-  </si>
-  <si>
-    <t>p20002_i0_a13</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 13</t>
-  </si>
-  <si>
-    <t>p20002_i0_a14</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 14</t>
-  </si>
-  <si>
-    <t>p20002_i0_a15</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 15</t>
-  </si>
-  <si>
-    <t>p20002_i0_a16</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 16</t>
-  </si>
-  <si>
-    <t>p20002_i0_a17</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 17</t>
-  </si>
-  <si>
-    <t>p20002_i0_a18</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 18</t>
-  </si>
-  <si>
-    <t>p20002_i0_a19</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 19</t>
-  </si>
-  <si>
-    <t>p20002_i0_a20</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 20</t>
-  </si>
-  <si>
-    <t>p20002_i0_a21</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 21</t>
-  </si>
-  <si>
-    <t>p20002_i0_a22</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 22</t>
-  </si>
-  <si>
-    <t>p20002_i0_a23</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 23</t>
-  </si>
-  <si>
-    <t>p20002_i0_a24</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 24</t>
-  </si>
-  <si>
-    <t>p20002_i0_a25</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 25</t>
-  </si>
-  <si>
-    <t>p20002_i0_a26</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 26</t>
-  </si>
-  <si>
-    <t>p20002_i0_a27</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 27</t>
-  </si>
-  <si>
-    <t>p20002_i0_a28</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 28</t>
-  </si>
-  <si>
-    <t>p20002_i0_a29</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 29</t>
-  </si>
-  <si>
-    <t>p20002_i0_a30</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 30</t>
-  </si>
-  <si>
-    <t>p20002_i0_a31</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 31</t>
-  </si>
-  <si>
-    <t>p20002_i0_a32</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 32</t>
-  </si>
-  <si>
-    <t>p20002_i0_a33</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 0 | Array 33</t>
-  </si>
-  <si>
-    <t>p20002_i1_a0</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 0</t>
-  </si>
-  <si>
-    <t>p20002_i1_a1</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 1</t>
-  </si>
-  <si>
-    <t>p20002_i1_a2</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 2</t>
-  </si>
-  <si>
-    <t>p20002_i1_a3</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 3</t>
-  </si>
-  <si>
-    <t>p20002_i1_a4</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 4</t>
-  </si>
-  <si>
-    <t>p20002_i1_a5</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 5</t>
-  </si>
-  <si>
-    <t>p20002_i1_a6</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 6</t>
-  </si>
-  <si>
-    <t>p20002_i1_a7</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 7</t>
-  </si>
-  <si>
-    <t>p20002_i1_a8</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 8</t>
-  </si>
-  <si>
-    <t>p20002_i1_a9</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 9</t>
-  </si>
-  <si>
-    <t>p20002_i1_a10</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 10</t>
-  </si>
-  <si>
-    <t>p20002_i1_a11</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 11</t>
-  </si>
-  <si>
-    <t>p20002_i1_a12</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 12</t>
-  </si>
-  <si>
-    <t>p20002_i1_a13</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 13</t>
-  </si>
-  <si>
-    <t>p20002_i1_a14</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 14</t>
-  </si>
-  <si>
-    <t>p20002_i1_a15</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 15</t>
-  </si>
-  <si>
-    <t>p20002_i1_a16</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 16</t>
-  </si>
-  <si>
-    <t>p20002_i1_a17</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 17</t>
-  </si>
-  <si>
-    <t>p20002_i1_a18</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 18</t>
-  </si>
-  <si>
-    <t>p20002_i1_a19</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 19</t>
-  </si>
-  <si>
-    <t>p20002_i1_a20</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 20</t>
-  </si>
-  <si>
-    <t>p20002_i1_a21</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 21</t>
-  </si>
-  <si>
-    <t>p20002_i1_a22</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 22</t>
-  </si>
-  <si>
-    <t>p20002_i1_a23</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 23</t>
-  </si>
-  <si>
-    <t>p20002_i1_a24</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 24</t>
-  </si>
-  <si>
-    <t>p20002_i1_a25</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 25</t>
-  </si>
-  <si>
-    <t>p20002_i1_a26</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 26</t>
-  </si>
-  <si>
-    <t>p20002_i1_a27</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 27</t>
-  </si>
-  <si>
-    <t>p20002_i1_a28</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 28</t>
-  </si>
-  <si>
-    <t>p20002_i1_a29</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 29</t>
-  </si>
-  <si>
-    <t>p20002_i1_a30</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 30</t>
-  </si>
-  <si>
-    <t>p20002_i1_a31</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 31</t>
-  </si>
-  <si>
-    <t>p20002_i1_a32</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 32</t>
-  </si>
-  <si>
-    <t>p20002_i1_a33</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 1 | Array 33</t>
-  </si>
-  <si>
-    <t>p20002_i2_a0</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 0</t>
-  </si>
-  <si>
-    <t>p20002_i2_a1</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 1</t>
-  </si>
-  <si>
-    <t>p20002_i2_a2</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 2</t>
-  </si>
-  <si>
-    <t>p20002_i2_a3</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 3</t>
-  </si>
-  <si>
-    <t>p20002_i2_a4</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 4</t>
-  </si>
-  <si>
-    <t>p20002_i2_a5</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 5</t>
-  </si>
-  <si>
-    <t>p20002_i2_a6</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 6</t>
-  </si>
-  <si>
-    <t>p20002_i2_a7</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 7</t>
-  </si>
-  <si>
-    <t>p20002_i2_a8</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 8</t>
-  </si>
-  <si>
-    <t>p20002_i2_a9</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 9</t>
-  </si>
-  <si>
-    <t>p20002_i2_a10</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 10</t>
-  </si>
-  <si>
-    <t>p20002_i2_a11</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 11</t>
-  </si>
-  <si>
-    <t>p20002_i2_a12</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 12</t>
-  </si>
-  <si>
-    <t>p20002_i2_a13</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 13</t>
-  </si>
-  <si>
-    <t>p20002_i2_a14</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 14</t>
-  </si>
-  <si>
-    <t>p20002_i2_a15</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 15</t>
-  </si>
-  <si>
-    <t>p20002_i2_a16</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 16</t>
-  </si>
-  <si>
-    <t>p20002_i2_a17</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 17</t>
-  </si>
-  <si>
-    <t>p20002_i2_a18</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 18</t>
-  </si>
-  <si>
-    <t>p20002_i2_a19</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 19</t>
-  </si>
-  <si>
-    <t>p20002_i2_a20</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 20</t>
-  </si>
-  <si>
-    <t>p20002_i2_a21</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 21</t>
-  </si>
-  <si>
-    <t>p20002_i2_a22</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 22</t>
-  </si>
-  <si>
-    <t>p20002_i2_a23</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 23</t>
-  </si>
-  <si>
-    <t>p20002_i2_a24</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 24</t>
-  </si>
-  <si>
-    <t>p20002_i2_a25</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 25</t>
-  </si>
-  <si>
-    <t>p20002_i2_a26</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 26</t>
-  </si>
-  <si>
-    <t>p20002_i2_a27</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 27</t>
-  </si>
-  <si>
-    <t>p20002_i2_a28</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 28</t>
-  </si>
-  <si>
-    <t>p20002_i2_a29</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 29</t>
-  </si>
-  <si>
-    <t>p20002_i2_a30</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 30</t>
-  </si>
-  <si>
-    <t>p20002_i2_a31</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 31</t>
-  </si>
-  <si>
-    <t>p20002_i2_a32</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 32</t>
-  </si>
-  <si>
-    <t>p20002_i2_a33</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 2 | Array 33</t>
-  </si>
-  <si>
-    <t>p20002_i3_a0</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 0</t>
-  </si>
-  <si>
-    <t>p20002_i3_a1</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 1</t>
-  </si>
-  <si>
-    <t>p20002_i3_a2</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 2</t>
-  </si>
-  <si>
-    <t>p20002_i3_a3</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 3</t>
-  </si>
-  <si>
-    <t>p20002_i3_a4</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 4</t>
-  </si>
-  <si>
-    <t>p20002_i3_a5</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 5</t>
-  </si>
-  <si>
-    <t>p20002_i3_a6</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 6</t>
-  </si>
-  <si>
-    <t>p20002_i3_a7</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 7</t>
-  </si>
-  <si>
-    <t>p20002_i3_a8</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 8</t>
-  </si>
-  <si>
-    <t>p20002_i3_a9</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 9</t>
-  </si>
-  <si>
-    <t>p20002_i3_a10</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 10</t>
-  </si>
-  <si>
-    <t>p20002_i3_a11</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 11</t>
-  </si>
-  <si>
-    <t>p20002_i3_a12</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 12</t>
-  </si>
-  <si>
-    <t>p20002_i3_a13</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 13</t>
-  </si>
-  <si>
-    <t>p20002_i3_a14</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 14</t>
-  </si>
-  <si>
-    <t>p20002_i3_a15</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 15</t>
-  </si>
-  <si>
-    <t>p20002_i3_a16</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 16</t>
-  </si>
-  <si>
-    <t>p20002_i3_a17</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 17</t>
-  </si>
-  <si>
-    <t>p20002_i3_a18</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 18</t>
-  </si>
-  <si>
-    <t>p20002_i3_a19</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 19</t>
-  </si>
-  <si>
-    <t>p20002_i3_a20</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 20</t>
-  </si>
-  <si>
-    <t>p20002_i3_a21</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 21</t>
-  </si>
-  <si>
-    <t>p20002_i3_a22</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 22</t>
-  </si>
-  <si>
-    <t>p20002_i3_a23</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 23</t>
-  </si>
-  <si>
-    <t>p20002_i3_a24</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 24</t>
-  </si>
-  <si>
-    <t>p20002_i3_a25</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 25</t>
-  </si>
-  <si>
-    <t>p20002_i3_a26</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 26</t>
-  </si>
-  <si>
-    <t>p20002_i3_a27</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 27</t>
-  </si>
-  <si>
-    <t>p20002_i3_a28</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 28</t>
-  </si>
-  <si>
-    <t>p20002_i3_a29</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 29</t>
-  </si>
-  <si>
-    <t>p20002_i3_a30</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 30</t>
-  </si>
-  <si>
-    <t>p20002_i3_a31</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 31</t>
-  </si>
-  <si>
-    <t>p20002_i3_a32</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 32</t>
-  </si>
-  <si>
-    <t>p20002_i3_a33</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported | Instance 3 | Array 33</t>
-  </si>
-  <si>
-    <t>p41270</t>
-  </si>
-  <si>
-    <t>Diagnoses - ICD10</t>
-  </si>
-  <si>
-    <t>p41271</t>
-  </si>
-  <si>
-    <t>Diagnoses - ICD9</t>
-  </si>
-  <si>
-    <t>p1647_i0</t>
-  </si>
-  <si>
-    <t>Country of birth (UK/elsewhere) | Instance 0</t>
-  </si>
-  <si>
-    <t>p1647_i1</t>
-  </si>
-  <si>
-    <t>Country of birth (UK/elsewhere) | Instance 1</t>
-  </si>
-  <si>
-    <t>p1647_i2</t>
-  </si>
-  <si>
-    <t>Country of birth (UK/elsewhere) | Instance 2</t>
-  </si>
-  <si>
     <t>Data-fileds</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Description</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Table S2. UKBB data-fileds accessed to identify cases and controls and perform quality control.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sex; Coding Meaning: Categorical (single); 0, Female; 1, Male</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Genetic sex; Coding Meaning: Categorical (single); 0, Female; 1, Male</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Age at recruitment; Coding Meaning: Integer, Units of measurement are years</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Body mass index (BMI) | Instance 0-3; Coding Meaning: Continuous, units of measurement are Kg/m2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ethnic background | Instance 0-3; Coding Meaning: Categorical (single), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Genetic ethnic grouping; Coding Meaning: Categorical (single), 1, Caucasian, https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=1002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outliers for heterozygosity or missing rate; Coding Meaning: Categorical (single), 1, Yes, https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Smoking status | Instance 0-3; Coding Meaning: Categorical (single), -3, Prefer not to answer; 0, Never; 1, Previous; 2, Current</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alcohol intake frequency. | Instance 0-3; Coding Meaning: Categorical (single), 1, Daily or almost daily; 2, Three or four times a week; 3, Once or twice a week; 4, One to three times a month; 5, Special occasions only; 6, Never; -3, Prefer not to answer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Townsend deprivation index at recruitment; Coding Meaning: Continuous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Genotype measurement batch; Coding Meaning: Categorical (single), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=22000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Genetic principal components | Array 1-40; Coding Meaning: Continuous, units of measurement are Units</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Date of attending assessment centre | Instance 0-3; Coding Meaning: Date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Date of death | Instance 0-1; Coding Meaning: Date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Date of cancer diagnosis | Instance 0-21; Coding Meaning: Date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type of cancer: ICD10 | Instance 0-21; Coding Meaning: Categorical (single), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=19; docs\materials\ukb\ICD10_coding19.tsv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type of cancer: ICD9 | Instance 0-14; Coding Meaning: Categorical (single), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=87; docs\materials\ukb\ICD9_coding87.tsv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cancer code, self-reported | Instance 0-3; Coding Meaning: Categorical (multiple), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=3; docs\materials\ukb\Cancer_code_self_reported_coding3.tsv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Underlying (primary) cause of death: ICD10 | Instance 0-1; Coding Meaning: Categorical (single), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=19; docs\materials\ukb\ICD10_coding19.tsv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Contributory (secondary) causes of death: ICD10 | Instance 0-1; Coding Meaning: Categorical (single), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=19; docs\materials\ukb\ICD10_coding19.tsv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diagnoses - main ICD10; Coding Meaning: Categorical (multiple), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=19; docs\materials\ukb\ICD10_coding19.tsv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diagnoses - main ICD9; Coding Meaning: Categorical (multiple), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=87; docs\materials\ukb\ICD9_coding87.tsv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diagnoses - secondary ICD10; Coding Meaning: Categorical (multiple), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=19; docs\materials\ukb\ICD10_coding19.tsv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diagnoses - secondary ICD9; Coding Meaning: Categorical (multiple), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=87; docs\materials\ukb\ICD9_coding87.tsv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Non-cancer illness code, self-reported | Instance 0-3; Coding Meaning: Categorical (multiple), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=6, docs\materials\ukb\Non_cancer_illness_code_self_reported_coding6.tsv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diagnoses - ICD10; Coding Meaning: Categorical (multiple), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=19; docs\materials\ukb\ICD10_coding19.tsv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diagnoses - ICD9; Coding Meaning: Categorical (multiple), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=87; docs\materials\ukb\ICD9_coding87.tsv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Country of birth (UK/elsewhere) | Instance 0-2; Coding Meaning: Categorical (single), https://biobank.ndph.ox.ac.uk/showcase/coding.cgi?id=100420; 1, England; 2, Wales; 3, Scotland; 4, Northern Ireland; 5, Republic of Ireland; 6, Elsewhere; -1, Do not know; -3, Prefer not to answer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Descriptions</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3678,7 +1816,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3799,6 +1937,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4381,11 +2522,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E85E0DD2-F97D-4D73-B494-1E0809FA7723}">
-  <dimension ref="A1:H336"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="81.375" style="10" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="10" customWidth="1"/>
+    <col min="2" max="2" width="247.75" style="10" customWidth="1"/>
     <col min="3" max="3" width="13.125" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="23.5" style="1" customWidth="1"/>
@@ -4396,17 +2537,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>1119</v>
+      <c r="A1" s="16" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:8" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>1117</v>
+      <c r="A3" s="14" t="s">
+        <v>459</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1118</v>
+        <v>489</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="2"/>
@@ -4416,7 +2557,7 @@
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>457</v>
       </c>
       <c r="B4" s="12" t="s">
@@ -4424,2650 +2565,248 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>459</v>
+      <c r="A5" s="10">
+        <v>31</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>461</v>
+      <c r="A6" s="10">
+        <v>22001</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="10">
+        <v>21022</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>463</v>
       </c>
-      <c r="B7" s="12" t="s">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <v>21001</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>21000</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>465</v>
       </c>
-      <c r="B8" s="12" t="s">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
+        <v>22006</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>22027</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>467</v>
       </c>
-      <c r="B9" s="12" t="s">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>20116</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <v>1558</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>469</v>
       </c>
-      <c r="B10" s="12" t="s">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <v>22189</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
+        <v>22000</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="B11" s="12" t="s">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
+        <v>22009</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
+        <v>53</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="B12" s="12" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
+        <v>40000</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
+        <v>40005</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="B13" s="12" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="10">
+        <v>40006</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="10">
+        <v>40013</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="B14" s="12" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="10">
+        <v>20001</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="10">
+        <v>40001</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>479</v>
       </c>
-      <c r="B15" s="12" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="10">
+        <v>40002</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="10">
+        <v>41202</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="B16" s="12" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="10">
+        <v>41203</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="10">
+        <v>41204</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="B17" s="12" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="10">
+        <v>41205</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="10">
+        <v>20002</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="B18" s="12" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="10">
+        <v>41270</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="10">
+        <v>41271</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="B19" s="12" t="s">
+    </row>
+    <row r="32" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="41">
+        <v>1647</v>
+      </c>
+      <c r="B32" s="32" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>489</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>493</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>495</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>499</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>501</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>503</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>505</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>507</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>509</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>511</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>515</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>517</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>519</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>521</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>525</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>527</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>529</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>531</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>533</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
-        <v>535</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>537</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>539</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
-        <v>543</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>545</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>547</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>549</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>551</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>553</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
-        <v>555</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
-        <v>557</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
-        <v>559</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
-        <v>561</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
-        <v>563</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>565</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
-        <v>567</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
-        <v>571</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
-        <v>573</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
-        <v>575</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
-        <v>577</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
-        <v>579</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
-        <v>581</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
-        <v>583</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
-        <v>585</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
-        <v>587</v>
-      </c>
-      <c r="B69" s="12" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="12" t="s">
-        <v>589</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
-        <v>591</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
-        <v>593</v>
-      </c>
-      <c r="B72" s="12" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
-        <v>595</v>
-      </c>
-      <c r="B73" s="12" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="12" t="s">
-        <v>597</v>
-      </c>
-      <c r="B74" s="12" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
-        <v>599</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>601</v>
-      </c>
-      <c r="B76" s="12" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
-        <v>603</v>
-      </c>
-      <c r="B77" s="12" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
-        <v>605</v>
-      </c>
-      <c r="B78" s="12" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="12" t="s">
-        <v>607</v>
-      </c>
-      <c r="B79" s="12" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="12" t="s">
-        <v>609</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="12" t="s">
-        <v>611</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="s">
-        <v>613</v>
-      </c>
-      <c r="B82" s="12" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="12" t="s">
-        <v>615</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="12" t="s">
-        <v>617</v>
-      </c>
-      <c r="B84" s="12" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="12" t="s">
-        <v>619</v>
-      </c>
-      <c r="B85" s="12" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="12" t="s">
-        <v>621</v>
-      </c>
-      <c r="B86" s="12" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="12" t="s">
-        <v>623</v>
-      </c>
-      <c r="B87" s="12" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="12" t="s">
-        <v>625</v>
-      </c>
-      <c r="B88" s="12" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="12" t="s">
-        <v>627</v>
-      </c>
-      <c r="B89" s="12" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="12" t="s">
-        <v>629</v>
-      </c>
-      <c r="B90" s="12" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="12" t="s">
-        <v>631</v>
-      </c>
-      <c r="B91" s="12" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="12" t="s">
-        <v>633</v>
-      </c>
-      <c r="B92" s="12" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="12" t="s">
-        <v>635</v>
-      </c>
-      <c r="B93" s="12" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="12" t="s">
-        <v>637</v>
-      </c>
-      <c r="B94" s="12" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="12" t="s">
-        <v>639</v>
-      </c>
-      <c r="B95" s="12" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="12" t="s">
-        <v>641</v>
-      </c>
-      <c r="B96" s="12" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="12" t="s">
-        <v>643</v>
-      </c>
-      <c r="B97" s="12" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="12" t="s">
-        <v>645</v>
-      </c>
-      <c r="B98" s="12" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="12" t="s">
-        <v>647</v>
-      </c>
-      <c r="B99" s="12" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="B100" s="12" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="12" t="s">
-        <v>651</v>
-      </c>
-      <c r="B101" s="12" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="12" t="s">
-        <v>653</v>
-      </c>
-      <c r="B102" s="12" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="12" t="s">
-        <v>655</v>
-      </c>
-      <c r="B103" s="12" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="12" t="s">
-        <v>657</v>
-      </c>
-      <c r="B104" s="12" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="12" t="s">
-        <v>659</v>
-      </c>
-      <c r="B105" s="12" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="12" t="s">
-        <v>661</v>
-      </c>
-      <c r="B106" s="12" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="12" t="s">
-        <v>663</v>
-      </c>
-      <c r="B107" s="12" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="12" t="s">
-        <v>665</v>
-      </c>
-      <c r="B108" s="12" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="12" t="s">
-        <v>667</v>
-      </c>
-      <c r="B109" s="12" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="12" t="s">
-        <v>669</v>
-      </c>
-      <c r="B110" s="12" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="12" t="s">
-        <v>671</v>
-      </c>
-      <c r="B111" s="12" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="12" t="s">
-        <v>673</v>
-      </c>
-      <c r="B112" s="12" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="B113" s="12" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="12" t="s">
-        <v>677</v>
-      </c>
-      <c r="B114" s="12" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="12" t="s">
-        <v>679</v>
-      </c>
-      <c r="B115" s="12" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="12" t="s">
-        <v>681</v>
-      </c>
-      <c r="B116" s="12" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="12" t="s">
-        <v>683</v>
-      </c>
-      <c r="B117" s="12" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="12" t="s">
-        <v>685</v>
-      </c>
-      <c r="B118" s="12" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="12" t="s">
-        <v>687</v>
-      </c>
-      <c r="B119" s="12" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="12" t="s">
-        <v>689</v>
-      </c>
-      <c r="B120" s="12" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="12" t="s">
-        <v>691</v>
-      </c>
-      <c r="B121" s="12" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="12" t="s">
-        <v>693</v>
-      </c>
-      <c r="B122" s="12" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="12" t="s">
-        <v>695</v>
-      </c>
-      <c r="B123" s="12" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="12" t="s">
-        <v>697</v>
-      </c>
-      <c r="B124" s="12" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="12" t="s">
-        <v>699</v>
-      </c>
-      <c r="B125" s="12" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="12" t="s">
-        <v>701</v>
-      </c>
-      <c r="B126" s="12" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="12" t="s">
-        <v>703</v>
-      </c>
-      <c r="B127" s="12" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="12" t="s">
-        <v>705</v>
-      </c>
-      <c r="B128" s="12" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="12" t="s">
-        <v>707</v>
-      </c>
-      <c r="B129" s="12" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="12" t="s">
-        <v>709</v>
-      </c>
-      <c r="B130" s="12" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="12" t="s">
-        <v>711</v>
-      </c>
-      <c r="B131" s="12" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="12" t="s">
-        <v>713</v>
-      </c>
-      <c r="B132" s="12" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="12" t="s">
-        <v>715</v>
-      </c>
-      <c r="B133" s="12" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="12" t="s">
-        <v>717</v>
-      </c>
-      <c r="B134" s="12" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="12" t="s">
-        <v>719</v>
-      </c>
-      <c r="B135" s="12" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="12" t="s">
-        <v>721</v>
-      </c>
-      <c r="B136" s="12" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="12" t="s">
-        <v>723</v>
-      </c>
-      <c r="B137" s="12" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="12" t="s">
-        <v>725</v>
-      </c>
-      <c r="B138" s="12" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="B139" s="12" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="12" t="s">
-        <v>729</v>
-      </c>
-      <c r="B140" s="12" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="12" t="s">
-        <v>731</v>
-      </c>
-      <c r="B141" s="12" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="12" t="s">
-        <v>733</v>
-      </c>
-      <c r="B142" s="12" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="12" t="s">
-        <v>735</v>
-      </c>
-      <c r="B143" s="12" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" s="12" t="s">
-        <v>737</v>
-      </c>
-      <c r="B144" s="12" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" s="12" t="s">
-        <v>739</v>
-      </c>
-      <c r="B145" s="12" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" s="12" t="s">
-        <v>741</v>
-      </c>
-      <c r="B146" s="12" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" s="12" t="s">
-        <v>743</v>
-      </c>
-      <c r="B147" s="12" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" s="12" t="s">
-        <v>745</v>
-      </c>
-      <c r="B148" s="12" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" s="12" t="s">
-        <v>747</v>
-      </c>
-      <c r="B149" s="12" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" s="12" t="s">
-        <v>749</v>
-      </c>
-      <c r="B150" s="12" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="B151" s="12" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" s="12" t="s">
-        <v>753</v>
-      </c>
-      <c r="B152" s="12" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" s="12" t="s">
-        <v>755</v>
-      </c>
-      <c r="B153" s="12" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" s="12" t="s">
-        <v>757</v>
-      </c>
-      <c r="B154" s="12" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" s="12" t="s">
-        <v>759</v>
-      </c>
-      <c r="B155" s="12" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" s="12" t="s">
-        <v>761</v>
-      </c>
-      <c r="B156" s="12" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" s="12" t="s">
-        <v>763</v>
-      </c>
-      <c r="B157" s="12" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" s="12" t="s">
-        <v>765</v>
-      </c>
-      <c r="B158" s="12" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" s="12" t="s">
-        <v>767</v>
-      </c>
-      <c r="B159" s="12" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A160" s="12" t="s">
-        <v>769</v>
-      </c>
-      <c r="B160" s="12" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" s="12" t="s">
-        <v>771</v>
-      </c>
-      <c r="B161" s="12" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" s="12" t="s">
-        <v>773</v>
-      </c>
-      <c r="B162" s="12" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" s="12" t="s">
-        <v>775</v>
-      </c>
-      <c r="B163" s="12" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" s="12" t="s">
-        <v>777</v>
-      </c>
-      <c r="B164" s="12" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" s="12" t="s">
-        <v>779</v>
-      </c>
-      <c r="B165" s="12" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" s="12" t="s">
-        <v>781</v>
-      </c>
-      <c r="B166" s="12" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A167" s="12" t="s">
-        <v>783</v>
-      </c>
-      <c r="B167" s="12" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A168" s="12" t="s">
-        <v>785</v>
-      </c>
-      <c r="B168" s="12" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A169" s="12" t="s">
-        <v>787</v>
-      </c>
-      <c r="B169" s="12" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A170" s="12" t="s">
-        <v>789</v>
-      </c>
-      <c r="B170" s="12" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A171" s="12" t="s">
-        <v>791</v>
-      </c>
-      <c r="B171" s="12" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A172" s="12" t="s">
-        <v>793</v>
-      </c>
-      <c r="B172" s="12" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A173" s="12" t="s">
-        <v>795</v>
-      </c>
-      <c r="B173" s="12" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A174" s="12" t="s">
-        <v>797</v>
-      </c>
-      <c r="B174" s="12" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A175" s="12" t="s">
-        <v>799</v>
-      </c>
-      <c r="B175" s="12" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A176" s="12" t="s">
-        <v>801</v>
-      </c>
-      <c r="B176" s="12" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A177" s="12" t="s">
-        <v>803</v>
-      </c>
-      <c r="B177" s="12" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A178" s="12" t="s">
-        <v>805</v>
-      </c>
-      <c r="B178" s="12" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A179" s="12" t="s">
-        <v>807</v>
-      </c>
-      <c r="B179" s="12" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A180" s="12" t="s">
-        <v>809</v>
-      </c>
-      <c r="B180" s="12" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181" s="12" t="s">
-        <v>811</v>
-      </c>
-      <c r="B181" s="12" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A182" s="12" t="s">
-        <v>813</v>
-      </c>
-      <c r="B182" s="12" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A183" s="12" t="s">
-        <v>815</v>
-      </c>
-      <c r="B183" s="12" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A184" s="12" t="s">
-        <v>817</v>
-      </c>
-      <c r="B184" s="12" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A185" s="12" t="s">
-        <v>819</v>
-      </c>
-      <c r="B185" s="12" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A186" s="12" t="s">
-        <v>821</v>
-      </c>
-      <c r="B186" s="12" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A187" s="12" t="s">
-        <v>823</v>
-      </c>
-      <c r="B187" s="12" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A188" s="12" t="s">
-        <v>825</v>
-      </c>
-      <c r="B188" s="12" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A189" s="12" t="s">
-        <v>827</v>
-      </c>
-      <c r="B189" s="12" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A190" s="12" t="s">
-        <v>829</v>
-      </c>
-      <c r="B190" s="12" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A191" s="12" t="s">
-        <v>831</v>
-      </c>
-      <c r="B191" s="12" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A192" s="12" t="s">
-        <v>833</v>
-      </c>
-      <c r="B192" s="12" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A193" s="12" t="s">
-        <v>835</v>
-      </c>
-      <c r="B193" s="12" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A194" s="12" t="s">
-        <v>837</v>
-      </c>
-      <c r="B194" s="12" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A195" s="12" t="s">
-        <v>839</v>
-      </c>
-      <c r="B195" s="12" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A196" s="12" t="s">
-        <v>841</v>
-      </c>
-      <c r="B196" s="12" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A197" s="12" t="s">
-        <v>843</v>
-      </c>
-      <c r="B197" s="12" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A198" s="12" t="s">
-        <v>845</v>
-      </c>
-      <c r="B198" s="12" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A199" s="12" t="s">
-        <v>847</v>
-      </c>
-      <c r="B199" s="12" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A200" s="12" t="s">
-        <v>849</v>
-      </c>
-      <c r="B200" s="12" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A201" s="12" t="s">
-        <v>851</v>
-      </c>
-      <c r="B201" s="12" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A202" s="12" t="s">
-        <v>853</v>
-      </c>
-      <c r="B202" s="12" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A203" s="12" t="s">
-        <v>855</v>
-      </c>
-      <c r="B203" s="12" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A204" s="12" t="s">
-        <v>857</v>
-      </c>
-      <c r="B204" s="12" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A205" s="12" t="s">
-        <v>859</v>
-      </c>
-      <c r="B205" s="12" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A206" s="12" t="s">
-        <v>861</v>
-      </c>
-      <c r="B206" s="12" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A207" s="12" t="s">
-        <v>863</v>
-      </c>
-      <c r="B207" s="12" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A208" s="12" t="s">
-        <v>865</v>
-      </c>
-      <c r="B208" s="12" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A209" s="12" t="s">
-        <v>867</v>
-      </c>
-      <c r="B209" s="12" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A210" s="12" t="s">
-        <v>869</v>
-      </c>
-      <c r="B210" s="12" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A211" s="12" t="s">
-        <v>871</v>
-      </c>
-      <c r="B211" s="12" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A212" s="12" t="s">
-        <v>873</v>
-      </c>
-      <c r="B212" s="12" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A213" s="12" t="s">
-        <v>875</v>
-      </c>
-      <c r="B213" s="12" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A214" s="12" t="s">
-        <v>877</v>
-      </c>
-      <c r="B214" s="12" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A215" s="12" t="s">
-        <v>879</v>
-      </c>
-      <c r="B215" s="12" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A216" s="12" t="s">
-        <v>881</v>
-      </c>
-      <c r="B216" s="12" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A217" s="12" t="s">
-        <v>883</v>
-      </c>
-      <c r="B217" s="12" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A218" s="12" t="s">
-        <v>885</v>
-      </c>
-      <c r="B218" s="12" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A219" s="12" t="s">
-        <v>887</v>
-      </c>
-      <c r="B219" s="12" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A220" s="12" t="s">
-        <v>889</v>
-      </c>
-      <c r="B220" s="12" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A221" s="12" t="s">
-        <v>891</v>
-      </c>
-      <c r="B221" s="12" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A222" s="12" t="s">
-        <v>893</v>
-      </c>
-      <c r="B222" s="12" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A223" s="12" t="s">
-        <v>895</v>
-      </c>
-      <c r="B223" s="12" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A224" s="12" t="s">
-        <v>897</v>
-      </c>
-      <c r="B224" s="12" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A225" s="12" t="s">
-        <v>899</v>
-      </c>
-      <c r="B225" s="12" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A226" s="12" t="s">
-        <v>901</v>
-      </c>
-      <c r="B226" s="12" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A227" s="12" t="s">
-        <v>903</v>
-      </c>
-      <c r="B227" s="12" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A228" s="12" t="s">
-        <v>905</v>
-      </c>
-      <c r="B228" s="12" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A229" s="12" t="s">
-        <v>907</v>
-      </c>
-      <c r="B229" s="12" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A230" s="12" t="s">
-        <v>909</v>
-      </c>
-      <c r="B230" s="12" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A231" s="12" t="s">
-        <v>911</v>
-      </c>
-      <c r="B231" s="12" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A232" s="12" t="s">
-        <v>913</v>
-      </c>
-      <c r="B232" s="12" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A233" s="12" t="s">
-        <v>915</v>
-      </c>
-      <c r="B233" s="12" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A234" s="12" t="s">
-        <v>917</v>
-      </c>
-      <c r="B234" s="12" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A235" s="12" t="s">
-        <v>919</v>
-      </c>
-      <c r="B235" s="12" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A236" s="12" t="s">
-        <v>921</v>
-      </c>
-      <c r="B236" s="12" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A237" s="12" t="s">
-        <v>923</v>
-      </c>
-      <c r="B237" s="12" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A238" s="12" t="s">
-        <v>925</v>
-      </c>
-      <c r="B238" s="12" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A239" s="12" t="s">
-        <v>927</v>
-      </c>
-      <c r="B239" s="12" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A240" s="12" t="s">
-        <v>929</v>
-      </c>
-      <c r="B240" s="12" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A241" s="12" t="s">
-        <v>931</v>
-      </c>
-      <c r="B241" s="12" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A242" s="12" t="s">
-        <v>933</v>
-      </c>
-      <c r="B242" s="12" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A243" s="12" t="s">
-        <v>935</v>
-      </c>
-      <c r="B243" s="12" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A244" s="12" t="s">
-        <v>937</v>
-      </c>
-      <c r="B244" s="12" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A245" s="12" t="s">
-        <v>939</v>
-      </c>
-      <c r="B245" s="12" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A246" s="12" t="s">
-        <v>941</v>
-      </c>
-      <c r="B246" s="12" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A247" s="12" t="s">
-        <v>943</v>
-      </c>
-      <c r="B247" s="12" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A248" s="12" t="s">
-        <v>945</v>
-      </c>
-      <c r="B248" s="12" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A249" s="12" t="s">
-        <v>947</v>
-      </c>
-      <c r="B249" s="12" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A250" s="12" t="s">
-        <v>949</v>
-      </c>
-      <c r="B250" s="12" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A251" s="12" t="s">
-        <v>951</v>
-      </c>
-      <c r="B251" s="12" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A252" s="12" t="s">
-        <v>953</v>
-      </c>
-      <c r="B252" s="12" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A253" s="12" t="s">
-        <v>955</v>
-      </c>
-      <c r="B253" s="12" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A254" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="B254" s="12" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A255" s="12" t="s">
-        <v>959</v>
-      </c>
-      <c r="B255" s="12" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A256" s="12" t="s">
-        <v>961</v>
-      </c>
-      <c r="B256" s="12" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A257" s="12" t="s">
-        <v>963</v>
-      </c>
-      <c r="B257" s="12" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A258" s="12" t="s">
-        <v>965</v>
-      </c>
-      <c r="B258" s="12" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A259" s="12" t="s">
-        <v>967</v>
-      </c>
-      <c r="B259" s="12" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A260" s="12" t="s">
-        <v>969</v>
-      </c>
-      <c r="B260" s="12" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A261" s="12" t="s">
-        <v>971</v>
-      </c>
-      <c r="B261" s="12" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A262" s="12" t="s">
-        <v>973</v>
-      </c>
-      <c r="B262" s="12" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A263" s="12" t="s">
-        <v>975</v>
-      </c>
-      <c r="B263" s="12" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A264" s="12" t="s">
-        <v>977</v>
-      </c>
-      <c r="B264" s="12" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A265" s="12" t="s">
-        <v>979</v>
-      </c>
-      <c r="B265" s="12" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A266" s="12" t="s">
-        <v>981</v>
-      </c>
-      <c r="B266" s="12" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A267" s="12" t="s">
-        <v>983</v>
-      </c>
-      <c r="B267" s="12" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A268" s="12" t="s">
-        <v>985</v>
-      </c>
-      <c r="B268" s="12" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A269" s="12" t="s">
-        <v>987</v>
-      </c>
-      <c r="B269" s="12" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A270" s="12" t="s">
-        <v>989</v>
-      </c>
-      <c r="B270" s="12" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A271" s="12" t="s">
-        <v>991</v>
-      </c>
-      <c r="B271" s="12" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A272" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="B272" s="12" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A273" s="12" t="s">
-        <v>995</v>
-      </c>
-      <c r="B273" s="12" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A274" s="12" t="s">
-        <v>997</v>
-      </c>
-      <c r="B274" s="12" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A275" s="12" t="s">
-        <v>999</v>
-      </c>
-      <c r="B275" s="12" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A276" s="12" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B276" s="12" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A277" s="12" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B277" s="12" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A278" s="12" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B278" s="12" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A279" s="12" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B279" s="12" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A280" s="12" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B280" s="12" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A281" s="12" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B281" s="12" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A282" s="12" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B282" s="12" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A283" s="12" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B283" s="12" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A284" s="12" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B284" s="12" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A285" s="12" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B285" s="12" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A286" s="12" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B286" s="12" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A287" s="12" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B287" s="12" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A288" s="12" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B288" s="12" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A289" s="12" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B289" s="12" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A290" s="12" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B290" s="12" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A291" s="12" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B291" s="12" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A292" s="12" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B292" s="12" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A293" s="12" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B293" s="12" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A294" s="12" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B294" s="12" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A295" s="12" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B295" s="12" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A296" s="12" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B296" s="12" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A297" s="12" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B297" s="12" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A298" s="12" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B298" s="12" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A299" s="12" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B299" s="12" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A300" s="12" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B300" s="12" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A301" s="12" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B301" s="12" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A302" s="12" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B302" s="12" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A303" s="12" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B303" s="12" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A304" s="12" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B304" s="12" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A305" s="12" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B305" s="12" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A306" s="12" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B306" s="12" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A307" s="12" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B307" s="12" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A308" s="12" t="s">
-        <v>1065</v>
-      </c>
-      <c r="B308" s="12" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A309" s="12" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B309" s="12" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A310" s="12" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B310" s="12" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A311" s="12" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B311" s="12" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A312" s="12" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B312" s="12" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A313" s="12" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B313" s="12" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A314" s="12" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B314" s="12" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A315" s="12" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B315" s="12" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A316" s="12" t="s">
-        <v>1081</v>
-      </c>
-      <c r="B316" s="12" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A317" s="12" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B317" s="12" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A318" s="12" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B318" s="12" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A319" s="12" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B319" s="12" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A320" s="12" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B320" s="12" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A321" s="12" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B321" s="12" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A322" s="12" t="s">
-        <v>1093</v>
-      </c>
-      <c r="B322" s="12" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A323" s="12" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B323" s="12" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A324" s="12" t="s">
-        <v>1097</v>
-      </c>
-      <c r="B324" s="12" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A325" s="12" t="s">
-        <v>1099</v>
-      </c>
-      <c r="B325" s="12" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A326" s="12" t="s">
-        <v>1101</v>
-      </c>
-      <c r="B326" s="12" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A327" s="12" t="s">
-        <v>1103</v>
-      </c>
-      <c r="B327" s="12" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A328" s="12" t="s">
-        <v>1105</v>
-      </c>
-      <c r="B328" s="12" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A329" s="12" t="s">
-        <v>1107</v>
-      </c>
-      <c r="B329" s="12" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A330" s="12" t="s">
-        <v>1109</v>
-      </c>
-      <c r="B330" s="12" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A331" s="12" t="s">
-        <v>1111</v>
-      </c>
-      <c r="B331" s="12" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A332" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B332" s="12" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="333" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A333" s="32" t="s">
-        <v>1115</v>
-      </c>
-      <c r="B333" s="32" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A335" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A336" s="12" t="s">
-        <v>300</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11125,6 +6864,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064E03803A74B364DAEBC39F6C7EEC88B" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="49ce98d08d805b506bcc40b8f43aa161">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7096755d-09e2-49ab-9780-382f17a74ff2" xmlns:ns3="2496ba1d-a99b-4e00-82bd-3ea232f3a0a7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d262d534f3278ea9c672dc9f1d9c575b" ns2:_="" ns3:_="">
     <xsd:import namespace="7096755d-09e2-49ab-9780-382f17a74ff2"/>
@@ -11367,16 +7115,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9135FDFF-2234-4F0B-B4DA-2AE6D09006AB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EBA38C6-46F4-4280-94E3-1F9DA4BE2039}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11393,12 +7140,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9135FDFF-2234-4F0B-B4DA-2AE6D09006AB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/output/Tables/mmc1.xlsx
+++ b/output/Tables/mmc1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\luzh29\Library\Projects\WGS_GWAS_and_MR\output\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CA66F7-520E-44BA-9BB8-0EFFD13D540A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D8432C-2C63-4990-86F5-5E2B9B7EE633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="692" activeTab="1" xr2:uid="{B1B36BAE-942B-7148-AF58-4A36D0B24BEE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" tabRatio="692" activeTab="1" xr2:uid="{B1B36BAE-942B-7148-AF58-4A36D0B24BEE}"/>
   </bookViews>
   <sheets>
     <sheet name="Table S1" sheetId="49" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="501">
   <si>
     <t>Disease</t>
   </si>
@@ -1680,6 +1680,50 @@
   </si>
   <si>
     <t>Descriptions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interpolated Year when cancer first diagnosed | Instance 0-3; Coding Meaning: https://biobank.ndph.ox.ac.uk/showcase/field.cgi?id=20006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interpolated Age of participant when cancer first diagnosed | Instance 0-3; Coding Meaning: https://biobank.ndph.ox.ac.uk/showcase/field.cgi?id=20007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interpolated Year when non-cancer illness first diagnosed | Instance 0-3; Coding Meaning: https://biobank.ndph.ox.ac.uk/showcase/field.cgi?id=20008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interpolated Age of participant when non-cancer illness first diagnosed | Instance 0-3; Coding Meaning: https://biobank.ndph.ox.ac.uk/showcase/field.cgi?id=20009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Method of recording time when cancer first diagnosed | Instance 0-3; Coding Meaning: https://biobank.ndph.ox.ac.uk/showcase/field.cgi?id=20012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Method of recording time when non-cancer illness first diagnosed | Instance 0-3; Coding Meaning: https://biobank.ndph.ox.ac.uk/showcase/field.cgi?id=20013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Age at death | Instance 0-1; Coding Meaning: https://biobank.ndph.ox.ac.uk/showcase/field.cgi?id=40007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Age at cancer diagnosis | Instance 0-21; Coding Meaning: https://biobank.ndph.ox.ac.uk/showcase/field.cgi?id=40008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cancer year/age first occurred | Instance 0-3; Coding Meaning: https://biobank.ndph.ox.ac.uk/showcase/field.cgi?id=84</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Non-cancer illness year/age first occurred | Instance 0-3; Coding Meaning: https://biobank.ndph.ox.ac.uk/showcase/field.cgi?id=87</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cancer diagnosed by doctor | Instance 0-3; Coding Meaning: https://biobank.ndph.ox.ac.uk/showcase/field.cgi?id=2453</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1896,12 +1940,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1919,6 +1957,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1938,7 +1979,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2324,19 +2368,19 @@
       <c r="C5" s="20">
         <v>1800</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="34">
         <v>1255</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="G5" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="34">
         <v>203972</v>
       </c>
     </row>
@@ -2350,11 +2394,11 @@
       <c r="C6" s="20">
         <v>1801</v>
       </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
     </row>
     <row r="7" spans="1:8" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
@@ -2366,11 +2410,11 @@
       <c r="C7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
     </row>
     <row r="8" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
@@ -2385,10 +2429,10 @@
       <c r="D8" s="3">
         <v>6247</v>
       </c>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
@@ -2400,7 +2444,7 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="35"/>
+      <c r="H9" s="34"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
@@ -2415,16 +2459,16 @@
       <c r="D10" s="3">
         <v>2063</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="34">
         <v>5716</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="35"/>
+      <c r="H10" s="34"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
@@ -2439,10 +2483,10 @@
       <c r="D11" s="3">
         <v>1530</v>
       </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
     </row>
     <row r="12" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
@@ -2457,10 +2501,10 @@
       <c r="D12" s="4">
         <v>2269</v>
       </c>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
@@ -2522,7 +2566,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E85E0DD2-F97D-4D73-B494-1E0809FA7723}">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.75" style="10" customWidth="1"/>
@@ -2686,120 +2730,208 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
-        <v>40006</v>
+        <v>20006</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
-        <v>40013</v>
+        <v>20007</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
-        <v>20001</v>
+        <v>20008</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
-        <v>40001</v>
+        <v>20009</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
-        <v>40002</v>
+        <v>20012</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
-        <v>41202</v>
+        <v>20013</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
-        <v>41203</v>
+        <v>40007</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
-        <v>41204</v>
+        <v>40008</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
-        <v>41205</v>
+        <v>84</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
-        <v>20002</v>
+        <v>87</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
-        <v>41270</v>
+        <v>2453</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
+        <v>40006</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="10">
+        <v>40013</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="10">
+        <v>20001</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="10">
+        <v>40001</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="10">
+        <v>40002</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="10">
+        <v>41202</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="10">
+        <v>41203</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="10">
+        <v>41204</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="10">
+        <v>41205</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="10">
+        <v>20002</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="10">
+        <v>41270</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="10">
         <v>41271</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B42" s="12" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="41">
+    <row r="43" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="33">
         <v>1647</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="B43" s="30" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2832,7 +2964,7 @@
         <v>455</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="D1" s="30"/>
+      <c r="D1" s="28"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -2841,25 +2973,25 @@
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:9" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="40" t="s">
         <v>304</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="6" t="s">
         <v>129</v>
       </c>
@@ -2877,7 +3009,7 @@
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="37" t="s">
         <v>157</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -2886,7 +3018,7 @@
       <c r="C5" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="27" t="s">
         <v>164</v>
       </c>
       <c r="E5" s="2"/>
@@ -2898,7 +3030,7 @@
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39"/>
+      <c r="A6" s="38"/>
       <c r="B6" s="12" t="s">
         <v>167</v>
       </c>
@@ -2916,7 +3048,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39"/>
+      <c r="A7" s="38"/>
       <c r="B7" s="12" t="s">
         <v>131</v>
       </c>
@@ -2934,7 +3066,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="39"/>
+      <c r="A8" s="38"/>
       <c r="B8" s="12" t="s">
         <v>168</v>
       </c>
@@ -2952,7 +3084,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39"/>
+      <c r="A9" s="38"/>
       <c r="B9" s="12" t="s">
         <v>131</v>
       </c>
@@ -2970,7 +3102,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="39"/>
+      <c r="A10" s="38"/>
       <c r="B10" s="12" t="s">
         <v>297</v>
       </c>
@@ -2988,7 +3120,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="39"/>
+      <c r="A11" s="38"/>
       <c r="B11" s="12" t="s">
         <v>131</v>
       </c>
@@ -3006,7 +3138,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="39"/>
+      <c r="A12" s="38"/>
       <c r="B12" s="12" t="s">
         <v>158</v>
       </c>
@@ -3024,7 +3156,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="39"/>
+      <c r="A13" s="38"/>
       <c r="B13" s="12" t="s">
         <v>132</v>
       </c>
@@ -3042,7 +3174,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="39"/>
+      <c r="A14" s="38"/>
       <c r="B14" s="12" t="s">
         <v>133</v>
       </c>
@@ -3060,7 +3192,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="39"/>
+      <c r="A15" s="38"/>
       <c r="B15" s="12" t="s">
         <v>134</v>
       </c>
@@ -3078,7 +3210,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="39"/>
+      <c r="A16" s="38"/>
       <c r="B16" s="12" t="s">
         <v>135</v>
       </c>
@@ -3096,7 +3228,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="39"/>
+      <c r="A17" s="38"/>
       <c r="B17" s="12" t="s">
         <v>136</v>
       </c>
@@ -3114,7 +3246,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="39"/>
+      <c r="A18" s="38"/>
       <c r="B18" s="12" t="s">
         <v>137</v>
       </c>
@@ -3132,7 +3264,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="39"/>
+      <c r="A19" s="38"/>
       <c r="B19" s="12" t="s">
         <v>138</v>
       </c>
@@ -3150,7 +3282,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="39"/>
+      <c r="A20" s="38"/>
       <c r="B20" s="12" t="s">
         <v>159</v>
       </c>
@@ -3168,7 +3300,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39"/>
+      <c r="A21" s="38"/>
       <c r="B21" s="12" t="s">
         <v>139</v>
       </c>
@@ -3186,7 +3318,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="39"/>
+      <c r="A22" s="38"/>
       <c r="B22" s="12" t="s">
         <v>140</v>
       </c>
@@ -3204,7 +3336,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="39"/>
+      <c r="A23" s="38"/>
       <c r="B23" s="12" t="s">
         <v>160</v>
       </c>
@@ -3222,7 +3354,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="39"/>
+      <c r="A24" s="38"/>
       <c r="B24" s="12" t="s">
         <v>141</v>
       </c>
@@ -3240,7 +3372,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="39"/>
+      <c r="A25" s="38"/>
       <c r="B25" s="12" t="s">
         <v>142</v>
       </c>
@@ -3258,7 +3390,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="39"/>
+      <c r="A26" s="38"/>
       <c r="B26" s="12" t="s">
         <v>143</v>
       </c>
@@ -3276,7 +3408,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="39"/>
+      <c r="A27" s="38"/>
       <c r="B27" s="12" t="s">
         <v>138</v>
       </c>
@@ -3294,7 +3426,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="39"/>
+      <c r="A28" s="38"/>
       <c r="B28" s="12" t="s">
         <v>161</v>
       </c>
@@ -3312,7 +3444,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="39"/>
+      <c r="A29" s="38"/>
       <c r="B29" s="12" t="s">
         <v>144</v>
       </c>
@@ -3330,7 +3462,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="39"/>
+      <c r="A30" s="38"/>
       <c r="B30" s="12" t="s">
         <v>145</v>
       </c>
@@ -3348,7 +3480,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="39"/>
+      <c r="A31" s="38"/>
       <c r="B31" s="12" t="s">
         <v>146</v>
       </c>
@@ -3366,7 +3498,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="39"/>
+      <c r="A32" s="38"/>
       <c r="B32" s="12" t="s">
         <v>147</v>
       </c>
@@ -3384,7 +3516,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="39"/>
+      <c r="A33" s="38"/>
       <c r="B33" s="12" t="s">
         <v>148</v>
       </c>
@@ -3402,7 +3534,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="39"/>
+      <c r="A34" s="38"/>
       <c r="B34" s="12" t="s">
         <v>141</v>
       </c>
@@ -3420,7 +3552,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="39"/>
+      <c r="A35" s="38"/>
       <c r="B35" s="12" t="s">
         <v>138</v>
       </c>
@@ -3438,7 +3570,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="39"/>
+      <c r="A36" s="38"/>
       <c r="B36" s="12" t="s">
         <v>162</v>
       </c>
@@ -3456,7 +3588,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="39"/>
+      <c r="A37" s="38"/>
       <c r="B37" s="12" t="s">
         <v>149</v>
       </c>
@@ -3474,7 +3606,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="39"/>
+      <c r="A38" s="38"/>
       <c r="B38" s="12" t="s">
         <v>150</v>
       </c>
@@ -3492,7 +3624,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="39"/>
+      <c r="A39" s="38"/>
       <c r="B39" s="12" t="s">
         <v>138</v>
       </c>
@@ -3510,7 +3642,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="39"/>
+      <c r="A40" s="38"/>
       <c r="B40" s="12" t="s">
         <v>163</v>
       </c>
@@ -3528,7 +3660,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="39"/>
+      <c r="A41" s="38"/>
       <c r="B41" s="12" t="s">
         <v>151</v>
       </c>
@@ -3546,7 +3678,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="39"/>
+      <c r="A42" s="38"/>
       <c r="B42" s="12" t="s">
         <v>152</v>
       </c>
@@ -3564,7 +3696,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="39"/>
+      <c r="A43" s="38"/>
       <c r="B43" s="12" t="s">
         <v>153</v>
       </c>
@@ -3582,7 +3714,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="39"/>
+      <c r="A44" s="38"/>
       <c r="B44" s="12" t="s">
         <v>154</v>
       </c>
@@ -3600,7 +3732,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="39" t="s">
+      <c r="A45" s="38" t="s">
         <v>169</v>
       </c>
       <c r="B45" s="9" t="s">
@@ -3609,7 +3741,7 @@
       <c r="C45" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D45" s="30" t="s">
+      <c r="D45" s="28" t="s">
         <v>171</v>
       </c>
       <c r="E45" s="2"/>
@@ -3621,7 +3753,7 @@
       <c r="I45" s="2"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="39"/>
+      <c r="A46" s="38"/>
       <c r="B46" s="12" t="s">
         <v>167</v>
       </c>
@@ -3639,7 +3771,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="39"/>
+      <c r="A47" s="38"/>
       <c r="B47" s="12" t="s">
         <v>131</v>
       </c>
@@ -3657,7 +3789,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="A48" s="39"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="12" t="s">
         <v>168</v>
       </c>
@@ -3675,7 +3807,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="39"/>
+      <c r="A49" s="38"/>
       <c r="B49" s="12" t="s">
         <v>131</v>
       </c>
@@ -3693,7 +3825,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="39"/>
+      <c r="A50" s="38"/>
       <c r="B50" s="12" t="s">
         <v>297</v>
       </c>
@@ -3711,7 +3843,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="39"/>
+      <c r="A51" s="38"/>
       <c r="B51" s="12" t="s">
         <v>131</v>
       </c>
@@ -3729,7 +3861,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="39"/>
+      <c r="A52" s="38"/>
       <c r="B52" s="12" t="s">
         <v>158</v>
       </c>
@@ -3747,7 +3879,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="39"/>
+      <c r="A53" s="38"/>
       <c r="B53" s="12" t="s">
         <v>132</v>
       </c>
@@ -3765,7 +3897,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="39"/>
+      <c r="A54" s="38"/>
       <c r="B54" s="12" t="s">
         <v>133</v>
       </c>
@@ -3783,7 +3915,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="39"/>
+      <c r="A55" s="38"/>
       <c r="B55" s="12" t="s">
         <v>134</v>
       </c>
@@ -3801,7 +3933,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="39"/>
+      <c r="A56" s="38"/>
       <c r="B56" s="12" t="s">
         <v>135</v>
       </c>
@@ -3819,7 +3951,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="39"/>
+      <c r="A57" s="38"/>
       <c r="B57" s="12" t="s">
         <v>136</v>
       </c>
@@ -3837,7 +3969,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="39"/>
+      <c r="A58" s="38"/>
       <c r="B58" s="12" t="s">
         <v>137</v>
       </c>
@@ -3855,7 +3987,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="39"/>
+      <c r="A59" s="38"/>
       <c r="B59" s="12" t="s">
         <v>138</v>
       </c>
@@ -3873,7 +4005,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="39"/>
+      <c r="A60" s="38"/>
       <c r="B60" s="12" t="s">
         <v>159</v>
       </c>
@@ -3891,7 +4023,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="39"/>
+      <c r="A61" s="38"/>
       <c r="B61" s="12" t="s">
         <v>139</v>
       </c>
@@ -3909,7 +4041,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="39"/>
+      <c r="A62" s="38"/>
       <c r="B62" s="12" t="s">
         <v>140</v>
       </c>
@@ -3927,7 +4059,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="39"/>
+      <c r="A63" s="38"/>
       <c r="B63" s="12" t="s">
         <v>160</v>
       </c>
@@ -3945,7 +4077,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="39"/>
+      <c r="A64" s="38"/>
       <c r="B64" s="12" t="s">
         <v>141</v>
       </c>
@@ -3963,7 +4095,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="39"/>
+      <c r="A65" s="38"/>
       <c r="B65" s="12" t="s">
         <v>142</v>
       </c>
@@ -3981,7 +4113,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="39"/>
+      <c r="A66" s="38"/>
       <c r="B66" s="12" t="s">
         <v>143</v>
       </c>
@@ -3999,7 +4131,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="39"/>
+      <c r="A67" s="38"/>
       <c r="B67" s="12" t="s">
         <v>138</v>
       </c>
@@ -4017,7 +4149,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="39"/>
+      <c r="A68" s="38"/>
       <c r="B68" s="12" t="s">
         <v>161</v>
       </c>
@@ -4035,7 +4167,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="39"/>
+      <c r="A69" s="38"/>
       <c r="B69" s="12" t="s">
         <v>144</v>
       </c>
@@ -4053,7 +4185,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="39"/>
+      <c r="A70" s="38"/>
       <c r="B70" s="12" t="s">
         <v>145</v>
       </c>
@@ -4071,7 +4203,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="39"/>
+      <c r="A71" s="38"/>
       <c r="B71" s="12" t="s">
         <v>146</v>
       </c>
@@ -4089,7 +4221,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="39"/>
+      <c r="A72" s="38"/>
       <c r="B72" s="12" t="s">
         <v>147</v>
       </c>
@@ -4107,7 +4239,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="39"/>
+      <c r="A73" s="38"/>
       <c r="B73" s="12" t="s">
         <v>148</v>
       </c>
@@ -4125,7 +4257,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="39"/>
+      <c r="A74" s="38"/>
       <c r="B74" s="12" t="s">
         <v>141</v>
       </c>
@@ -4143,7 +4275,7 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="39"/>
+      <c r="A75" s="38"/>
       <c r="B75" s="12" t="s">
         <v>138</v>
       </c>
@@ -4161,7 +4293,7 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="39"/>
+      <c r="A76" s="38"/>
       <c r="B76" s="12" t="s">
         <v>162</v>
       </c>
@@ -4179,7 +4311,7 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="39"/>
+      <c r="A77" s="38"/>
       <c r="B77" s="12" t="s">
         <v>149</v>
       </c>
@@ -4197,7 +4329,7 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="39"/>
+      <c r="A78" s="38"/>
       <c r="B78" s="12" t="s">
         <v>150</v>
       </c>
@@ -4215,7 +4347,7 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="39"/>
+      <c r="A79" s="38"/>
       <c r="B79" s="12" t="s">
         <v>138</v>
       </c>
@@ -4233,7 +4365,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="39"/>
+      <c r="A80" s="38"/>
       <c r="B80" s="12" t="s">
         <v>163</v>
       </c>
@@ -4251,7 +4383,7 @@
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="39"/>
+      <c r="A81" s="38"/>
       <c r="B81" s="12" t="s">
         <v>151</v>
       </c>
@@ -4269,7 +4401,7 @@
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="39"/>
+      <c r="A82" s="38"/>
       <c r="B82" s="12" t="s">
         <v>152</v>
       </c>
@@ -4287,7 +4419,7 @@
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="39"/>
+      <c r="A83" s="38"/>
       <c r="B83" s="12" t="s">
         <v>153</v>
       </c>
@@ -4305,7 +4437,7 @@
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="39"/>
+      <c r="A84" s="38"/>
       <c r="B84" s="12" t="s">
         <v>154</v>
       </c>
@@ -4323,7 +4455,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="39" t="s">
+      <c r="A85" s="38" t="s">
         <v>236</v>
       </c>
       <c r="B85" s="9" t="s">
@@ -4332,7 +4464,7 @@
       <c r="C85" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D85" s="29" t="s">
+      <c r="D85" s="27" t="s">
         <v>171</v>
       </c>
       <c r="E85" s="2"/>
@@ -4344,14 +4476,14 @@
       <c r="I85" s="2"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="39"/>
+      <c r="A86" s="38"/>
       <c r="B86" s="12" t="s">
         <v>167</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D86" s="31" t="s">
+      <c r="D86" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E86" s="1" t="s">
@@ -4362,14 +4494,14 @@
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="39"/>
+      <c r="A87" s="38"/>
       <c r="B87" s="12" t="s">
         <v>131</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D87" s="31" t="s">
+      <c r="D87" s="29" t="s">
         <v>38</v>
       </c>
       <c r="E87" s="1" t="s">
@@ -4380,14 +4512,14 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="A88" s="39"/>
+      <c r="A88" s="38"/>
       <c r="B88" s="12" t="s">
         <v>168</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="31" t="s">
+      <c r="D88" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E88" s="1" t="s">
@@ -4398,14 +4530,14 @@
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="39"/>
+      <c r="A89" s="38"/>
       <c r="B89" s="12" t="s">
         <v>131</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D89" s="31" t="s">
+      <c r="D89" s="29" t="s">
         <v>41</v>
       </c>
       <c r="E89" s="1" t="s">
@@ -4416,14 +4548,14 @@
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="39"/>
+      <c r="A90" s="38"/>
       <c r="B90" s="12" t="s">
         <v>297</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D90" s="31" t="s">
+      <c r="D90" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E90" s="1" t="s">
@@ -4434,14 +4566,14 @@
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="39"/>
+      <c r="A91" s="38"/>
       <c r="B91" s="12" t="s">
         <v>131</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D91" s="31" t="s">
+      <c r="D91" s="29" t="s">
         <v>44</v>
       </c>
       <c r="E91" s="1" t="s">
@@ -4452,14 +4584,14 @@
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="39"/>
+      <c r="A92" s="38"/>
       <c r="B92" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D92" s="31" t="s">
+      <c r="D92" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E92" s="1" t="s">
@@ -4470,14 +4602,14 @@
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="39"/>
+      <c r="A93" s="38"/>
       <c r="B93" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D93" s="31" t="s">
+      <c r="D93" s="29" t="s">
         <v>47</v>
       </c>
       <c r="E93" s="1" t="s">
@@ -4488,14 +4620,14 @@
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="39"/>
+      <c r="A94" s="38"/>
       <c r="B94" s="12" t="s">
         <v>133</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D94" s="31" t="s">
+      <c r="D94" s="29" t="s">
         <v>50</v>
       </c>
       <c r="E94" s="1" t="s">
@@ -4506,14 +4638,14 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="39"/>
+      <c r="A95" s="38"/>
       <c r="B95" s="12" t="s">
         <v>134</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D95" s="31" t="s">
+      <c r="D95" s="29" t="s">
         <v>53</v>
       </c>
       <c r="E95" s="1" t="s">
@@ -4524,14 +4656,14 @@
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="39"/>
+      <c r="A96" s="38"/>
       <c r="B96" s="12" t="s">
         <v>135</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D96" s="31" t="s">
+      <c r="D96" s="29" t="s">
         <v>56</v>
       </c>
       <c r="E96" s="1" t="s">
@@ -4542,14 +4674,14 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="39"/>
+      <c r="A97" s="38"/>
       <c r="B97" s="12" t="s">
         <v>136</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D97" s="31" t="s">
+      <c r="D97" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E97" s="1" t="s">
@@ -4560,14 +4692,14 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="39"/>
+      <c r="A98" s="38"/>
       <c r="B98" s="12" t="s">
         <v>137</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D98" s="31" t="s">
+      <c r="D98" s="29" t="s">
         <v>62</v>
       </c>
       <c r="E98" s="1" t="s">
@@ -4578,14 +4710,14 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="39"/>
+      <c r="A99" s="38"/>
       <c r="B99" s="12" t="s">
         <v>138</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="D99" s="31" t="s">
+      <c r="D99" s="29" t="s">
         <v>65</v>
       </c>
       <c r="E99" s="1" t="s">
@@ -4596,14 +4728,14 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="39"/>
+      <c r="A100" s="38"/>
       <c r="B100" s="12" t="s">
         <v>159</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D100" s="31" t="s">
+      <c r="D100" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E100" s="1" t="s">
@@ -4614,14 +4746,14 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="39"/>
+      <c r="A101" s="38"/>
       <c r="B101" s="12" t="s">
         <v>139</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D101" s="31" t="s">
+      <c r="D101" s="29" t="s">
         <v>68</v>
       </c>
       <c r="E101" s="1" t="s">
@@ -4632,14 +4764,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="39"/>
+      <c r="A102" s="38"/>
       <c r="B102" s="12" t="s">
         <v>140</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D102" s="31" t="s">
+      <c r="D102" s="29" t="s">
         <v>71</v>
       </c>
       <c r="E102" s="1" t="s">
@@ -4650,14 +4782,14 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="39"/>
+      <c r="A103" s="38"/>
       <c r="B103" s="12" t="s">
         <v>160</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D103" s="31" t="s">
+      <c r="D103" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E103" s="1" t="s">
@@ -4668,14 +4800,14 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="39"/>
+      <c r="A104" s="38"/>
       <c r="B104" s="12" t="s">
         <v>141</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D104" s="31" t="s">
+      <c r="D104" s="29" t="s">
         <v>74</v>
       </c>
       <c r="E104" s="1" t="s">
@@ -4686,14 +4818,14 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="39"/>
+      <c r="A105" s="38"/>
       <c r="B105" s="12" t="s">
         <v>142</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D105" s="31" t="s">
+      <c r="D105" s="29" t="s">
         <v>77</v>
       </c>
       <c r="E105" s="1" t="s">
@@ -4704,14 +4836,14 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="39"/>
+      <c r="A106" s="38"/>
       <c r="B106" s="12" t="s">
         <v>143</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D106" s="31" t="s">
+      <c r="D106" s="29" t="s">
         <v>80</v>
       </c>
       <c r="E106" s="1" t="s">
@@ -4722,14 +4854,14 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="39"/>
+      <c r="A107" s="38"/>
       <c r="B107" s="12" t="s">
         <v>138</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D107" s="31" t="s">
+      <c r="D107" s="29" t="s">
         <v>83</v>
       </c>
       <c r="E107" s="1" t="s">
@@ -4740,14 +4872,14 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="39"/>
+      <c r="A108" s="38"/>
       <c r="B108" s="12" t="s">
         <v>161</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D108" s="31" t="s">
+      <c r="D108" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E108" s="1" t="s">
@@ -4758,14 +4890,14 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="39"/>
+      <c r="A109" s="38"/>
       <c r="B109" s="12" t="s">
         <v>144</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D109" s="31" t="s">
+      <c r="D109" s="29" t="s">
         <v>86</v>
       </c>
       <c r="E109" s="1" t="s">
@@ -4776,14 +4908,14 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="39"/>
+      <c r="A110" s="38"/>
       <c r="B110" s="12" t="s">
         <v>145</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D110" s="31" t="s">
+      <c r="D110" s="29" t="s">
         <v>89</v>
       </c>
       <c r="E110" s="1" t="s">
@@ -4794,14 +4926,14 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="39"/>
+      <c r="A111" s="38"/>
       <c r="B111" s="12" t="s">
         <v>146</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D111" s="31" t="s">
+      <c r="D111" s="29" t="s">
         <v>92</v>
       </c>
       <c r="E111" s="1" t="s">
@@ -4812,14 +4944,14 @@
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="39"/>
+      <c r="A112" s="38"/>
       <c r="B112" s="12" t="s">
         <v>147</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D112" s="31" t="s">
+      <c r="D112" s="29" t="s">
         <v>95</v>
       </c>
       <c r="E112" s="1" t="s">
@@ -4830,14 +4962,14 @@
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="39"/>
+      <c r="A113" s="38"/>
       <c r="B113" s="12" t="s">
         <v>148</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D113" s="31" t="s">
+      <c r="D113" s="29" t="s">
         <v>98</v>
       </c>
       <c r="E113" s="1" t="s">
@@ -4848,14 +4980,14 @@
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="39"/>
+      <c r="A114" s="38"/>
       <c r="B114" s="12" t="s">
         <v>141</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D114" s="31" t="s">
+      <c r="D114" s="29" t="s">
         <v>101</v>
       </c>
       <c r="E114" s="1" t="s">
@@ -4866,14 +4998,14 @@
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="39"/>
+      <c r="A115" s="38"/>
       <c r="B115" s="12" t="s">
         <v>138</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D115" s="31" t="s">
+      <c r="D115" s="29" t="s">
         <v>104</v>
       </c>
       <c r="E115" s="1" t="s">
@@ -4884,14 +5016,14 @@
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="39"/>
+      <c r="A116" s="38"/>
       <c r="B116" s="12" t="s">
         <v>162</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D116" s="31" t="s">
+      <c r="D116" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E116" s="1" t="s">
@@ -4902,14 +5034,14 @@
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="39"/>
+      <c r="A117" s="38"/>
       <c r="B117" s="12" t="s">
         <v>149</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D117" s="31" t="s">
+      <c r="D117" s="29" t="s">
         <v>107</v>
       </c>
       <c r="E117" s="1" t="s">
@@ -4920,14 +5052,14 @@
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="39"/>
+      <c r="A118" s="38"/>
       <c r="B118" s="12" t="s">
         <v>150</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D118" s="31" t="s">
+      <c r="D118" s="29" t="s">
         <v>110</v>
       </c>
       <c r="E118" s="1" t="s">
@@ -4938,14 +5070,14 @@
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="39"/>
+      <c r="A119" s="38"/>
       <c r="B119" s="12" t="s">
         <v>138</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D119" s="31" t="s">
+      <c r="D119" s="29" t="s">
         <v>113</v>
       </c>
       <c r="E119" s="1" t="s">
@@ -4956,14 +5088,14 @@
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="39"/>
+      <c r="A120" s="38"/>
       <c r="B120" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D120" s="31" t="s">
+      <c r="D120" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E120" s="1" t="s">
@@ -4974,14 +5106,14 @@
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="39"/>
+      <c r="A121" s="38"/>
       <c r="B121" s="12" t="s">
         <v>151</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D121" s="31" t="s">
+      <c r="D121" s="29" t="s">
         <v>116</v>
       </c>
       <c r="E121" s="1" t="s">
@@ -4992,14 +5124,14 @@
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="39"/>
+      <c r="A122" s="38"/>
       <c r="B122" s="12" t="s">
         <v>152</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="D122" s="31" t="s">
+      <c r="D122" s="29" t="s">
         <v>119</v>
       </c>
       <c r="E122" s="1" t="s">
@@ -5010,14 +5142,14 @@
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="39"/>
+      <c r="A123" s="38"/>
       <c r="B123" s="12" t="s">
         <v>153</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="D123" s="31" t="s">
+      <c r="D123" s="29" t="s">
         <v>122</v>
       </c>
       <c r="E123" s="1" t="s">
@@ -5028,20 +5160,20 @@
       </c>
     </row>
     <row r="124" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="40"/>
-      <c r="B124" s="32" t="s">
+      <c r="A124" s="39"/>
+      <c r="B124" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="C124" s="33" t="s">
+      <c r="C124" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="D124" s="34" t="s">
+      <c r="D124" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="E124" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="F124" s="33" t="s">
+      <c r="E124" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="F124" s="31" t="s">
         <v>296</v>
       </c>
     </row>
@@ -5118,11 +5250,13 @@
       <c r="I133" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="A5:A44"/>
     <mergeCell ref="A45:A84"/>
     <mergeCell ref="A85:A124"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5151,7 +5285,7 @@
         <v>456</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="D1" s="30"/>
+      <c r="D1" s="28"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -5160,25 +5294,25 @@
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:9" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="40" t="s">
         <v>304</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="6" t="s">
         <v>129</v>
       </c>
@@ -5196,7 +5330,7 @@
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="37" t="s">
         <v>157</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -5205,7 +5339,7 @@
       <c r="C5" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="27" t="s">
         <v>308</v>
       </c>
       <c r="E5" s="2"/>
@@ -5217,7 +5351,7 @@
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39"/>
+      <c r="A6" s="38"/>
       <c r="B6" s="12" t="s">
         <v>167</v>
       </c>
@@ -5235,7 +5369,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39"/>
+      <c r="A7" s="38"/>
       <c r="B7" s="12" t="s">
         <v>131</v>
       </c>
@@ -5253,7 +5387,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="39"/>
+      <c r="A8" s="38"/>
       <c r="B8" s="12" t="s">
         <v>168</v>
       </c>
@@ -5271,7 +5405,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39"/>
+      <c r="A9" s="38"/>
       <c r="B9" s="12" t="s">
         <v>131</v>
       </c>
@@ -5289,7 +5423,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="39"/>
+      <c r="A10" s="38"/>
       <c r="B10" s="12" t="s">
         <v>297</v>
       </c>
@@ -5307,7 +5441,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="39"/>
+      <c r="A11" s="38"/>
       <c r="B11" s="12" t="s">
         <v>131</v>
       </c>
@@ -5325,7 +5459,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="39"/>
+      <c r="A12" s="38"/>
       <c r="B12" s="12" t="s">
         <v>160</v>
       </c>
@@ -5343,7 +5477,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="39"/>
+      <c r="A13" s="38"/>
       <c r="B13" s="12" t="s">
         <v>141</v>
       </c>
@@ -5361,7 +5495,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="39"/>
+      <c r="A14" s="38"/>
       <c r="B14" s="12" t="s">
         <v>142</v>
       </c>
@@ -5379,7 +5513,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="39"/>
+      <c r="A15" s="38"/>
       <c r="B15" s="12" t="s">
         <v>143</v>
       </c>
@@ -5397,7 +5531,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="39"/>
+      <c r="A16" s="38"/>
       <c r="B16" s="12" t="s">
         <v>138</v>
       </c>
@@ -5415,7 +5549,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="39"/>
+      <c r="A17" s="38"/>
       <c r="B17" s="12" t="s">
         <v>161</v>
       </c>
@@ -5433,7 +5567,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="39"/>
+      <c r="A18" s="38"/>
       <c r="B18" s="12" t="s">
         <v>144</v>
       </c>
@@ -5451,7 +5585,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="39"/>
+      <c r="A19" s="38"/>
       <c r="B19" s="12" t="s">
         <v>145</v>
       </c>
@@ -5469,7 +5603,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="39"/>
+      <c r="A20" s="38"/>
       <c r="B20" s="12" t="s">
         <v>146</v>
       </c>
@@ -5487,7 +5621,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39"/>
+      <c r="A21" s="38"/>
       <c r="B21" s="12" t="s">
         <v>147</v>
       </c>
@@ -5505,7 +5639,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="39"/>
+      <c r="A22" s="38"/>
       <c r="B22" s="12" t="s">
         <v>148</v>
       </c>
@@ -5523,7 +5657,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="39"/>
+      <c r="A23" s="38"/>
       <c r="B23" s="12" t="s">
         <v>141</v>
       </c>
@@ -5541,7 +5675,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="39"/>
+      <c r="A24" s="38"/>
       <c r="B24" s="12" t="s">
         <v>138</v>
       </c>
@@ -5559,7 +5693,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="39"/>
+      <c r="A25" s="38"/>
       <c r="B25" s="12" t="s">
         <v>162</v>
       </c>
@@ -5577,7 +5711,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="39"/>
+      <c r="A26" s="38"/>
       <c r="B26" s="12" t="s">
         <v>149</v>
       </c>
@@ -5595,7 +5729,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="39"/>
+      <c r="A27" s="38"/>
       <c r="B27" s="12" t="s">
         <v>150</v>
       </c>
@@ -5613,7 +5747,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="39"/>
+      <c r="A28" s="38"/>
       <c r="B28" s="12" t="s">
         <v>138</v>
       </c>
@@ -5631,7 +5765,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="39"/>
+      <c r="A29" s="38"/>
       <c r="B29" s="12" t="s">
         <v>163</v>
       </c>
@@ -5649,7 +5783,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="39"/>
+      <c r="A30" s="38"/>
       <c r="B30" s="12" t="s">
         <v>151</v>
       </c>
@@ -5667,7 +5801,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="39"/>
+      <c r="A31" s="38"/>
       <c r="B31" s="12" t="s">
         <v>152</v>
       </c>
@@ -5685,7 +5819,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="39"/>
+      <c r="A32" s="38"/>
       <c r="B32" s="12" t="s">
         <v>153</v>
       </c>
@@ -5703,7 +5837,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="39"/>
+      <c r="A33" s="38"/>
       <c r="B33" s="12" t="s">
         <v>154</v>
       </c>
@@ -5721,7 +5855,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="39" t="s">
+      <c r="A34" s="38" t="s">
         <v>169</v>
       </c>
       <c r="B34" s="9" t="s">
@@ -5730,7 +5864,7 @@
       <c r="C34" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="28" t="s">
         <v>308</v>
       </c>
       <c r="E34" s="2"/>
@@ -5742,7 +5876,7 @@
       <c r="I34" s="2"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="39"/>
+      <c r="A35" s="38"/>
       <c r="B35" s="12" t="s">
         <v>167</v>
       </c>
@@ -5760,7 +5894,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="39"/>
+      <c r="A36" s="38"/>
       <c r="B36" s="12" t="s">
         <v>131</v>
       </c>
@@ -5778,7 +5912,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="A37" s="39"/>
+      <c r="A37" s="38"/>
       <c r="B37" s="12" t="s">
         <v>168</v>
       </c>
@@ -5796,7 +5930,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="39"/>
+      <c r="A38" s="38"/>
       <c r="B38" s="12" t="s">
         <v>131</v>
       </c>
@@ -5814,7 +5948,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="39"/>
+      <c r="A39" s="38"/>
       <c r="B39" s="12" t="s">
         <v>297</v>
       </c>
@@ -5832,7 +5966,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="39"/>
+      <c r="A40" s="38"/>
       <c r="B40" s="12" t="s">
         <v>131</v>
       </c>
@@ -5850,7 +5984,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="39"/>
+      <c r="A41" s="38"/>
       <c r="B41" s="12" t="s">
         <v>160</v>
       </c>
@@ -5868,7 +6002,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="39"/>
+      <c r="A42" s="38"/>
       <c r="B42" s="12" t="s">
         <v>141</v>
       </c>
@@ -5886,7 +6020,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="39"/>
+      <c r="A43" s="38"/>
       <c r="B43" s="12" t="s">
         <v>142</v>
       </c>
@@ -5904,7 +6038,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="39"/>
+      <c r="A44" s="38"/>
       <c r="B44" s="12" t="s">
         <v>143</v>
       </c>
@@ -5922,7 +6056,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="39"/>
+      <c r="A45" s="38"/>
       <c r="B45" s="12" t="s">
         <v>138</v>
       </c>
@@ -5940,7 +6074,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="39"/>
+      <c r="A46" s="38"/>
       <c r="B46" s="12" t="s">
         <v>161</v>
       </c>
@@ -5958,7 +6092,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="39"/>
+      <c r="A47" s="38"/>
       <c r="B47" s="12" t="s">
         <v>144</v>
       </c>
@@ -5976,7 +6110,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="39"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="12" t="s">
         <v>145</v>
       </c>
@@ -5994,7 +6128,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="39"/>
+      <c r="A49" s="38"/>
       <c r="B49" s="12" t="s">
         <v>146</v>
       </c>
@@ -6012,7 +6146,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="39"/>
+      <c r="A50" s="38"/>
       <c r="B50" s="12" t="s">
         <v>147</v>
       </c>
@@ -6030,7 +6164,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="39"/>
+      <c r="A51" s="38"/>
       <c r="B51" s="12" t="s">
         <v>148</v>
       </c>
@@ -6048,7 +6182,7 @@
       </c>
     </row>
     <row r="52" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="39"/>
+      <c r="A52" s="38"/>
       <c r="B52" s="12" t="s">
         <v>141</v>
       </c>
@@ -6066,7 +6200,7 @@
       </c>
     </row>
     <row r="53" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="39"/>
+      <c r="A53" s="38"/>
       <c r="B53" s="12" t="s">
         <v>138</v>
       </c>
@@ -6084,7 +6218,7 @@
       </c>
     </row>
     <row r="54" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="39"/>
+      <c r="A54" s="38"/>
       <c r="B54" s="12" t="s">
         <v>162</v>
       </c>
@@ -6102,7 +6236,7 @@
       </c>
     </row>
     <row r="55" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="39"/>
+      <c r="A55" s="38"/>
       <c r="B55" s="12" t="s">
         <v>149</v>
       </c>
@@ -6120,7 +6254,7 @@
       </c>
     </row>
     <row r="56" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="39"/>
+      <c r="A56" s="38"/>
       <c r="B56" s="12" t="s">
         <v>150</v>
       </c>
@@ -6138,7 +6272,7 @@
       </c>
     </row>
     <row r="57" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="39"/>
+      <c r="A57" s="38"/>
       <c r="B57" s="12" t="s">
         <v>138</v>
       </c>
@@ -6156,7 +6290,7 @@
       </c>
     </row>
     <row r="58" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="39"/>
+      <c r="A58" s="38"/>
       <c r="B58" s="12" t="s">
         <v>163</v>
       </c>
@@ -6174,7 +6308,7 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="39"/>
+      <c r="A59" s="38"/>
       <c r="B59" s="12" t="s">
         <v>151</v>
       </c>
@@ -6192,7 +6326,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="39"/>
+      <c r="A60" s="38"/>
       <c r="B60" s="12" t="s">
         <v>152</v>
       </c>
@@ -6210,7 +6344,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="39"/>
+      <c r="A61" s="38"/>
       <c r="B61" s="12" t="s">
         <v>153</v>
       </c>
@@ -6228,7 +6362,7 @@
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="39"/>
+      <c r="A62" s="38"/>
       <c r="B62" s="12" t="s">
         <v>154</v>
       </c>
@@ -6246,7 +6380,7 @@
       </c>
     </row>
     <row r="63" spans="1:9" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="39" t="s">
+      <c r="A63" s="38" t="s">
         <v>236</v>
       </c>
       <c r="B63" s="9" t="s">
@@ -6255,7 +6389,7 @@
       <c r="C63" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="D63" s="29" t="s">
+      <c r="D63" s="27" t="s">
         <v>308</v>
       </c>
       <c r="E63" s="2"/>
@@ -6267,14 +6401,14 @@
       <c r="I63" s="2"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="39"/>
+      <c r="A64" s="38"/>
       <c r="B64" s="12" t="s">
         <v>167</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D64" s="31" t="s">
+      <c r="D64" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E64" s="1" t="s">
@@ -6285,14 +6419,14 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="39"/>
+      <c r="A65" s="38"/>
       <c r="B65" s="12" t="s">
         <v>131</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D65" s="31" t="s">
+      <c r="D65" s="29" t="s">
         <v>311</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -6303,14 +6437,14 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="A66" s="39"/>
+      <c r="A66" s="38"/>
       <c r="B66" s="12" t="s">
         <v>168</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D66" s="31" t="s">
+      <c r="D66" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -6321,14 +6455,14 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="39"/>
+      <c r="A67" s="38"/>
       <c r="B67" s="12" t="s">
         <v>131</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="D67" s="31" t="s">
+      <c r="D67" s="29" t="s">
         <v>314</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -6339,14 +6473,14 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="39"/>
+      <c r="A68" s="38"/>
       <c r="B68" s="12" t="s">
         <v>297</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D68" s="31" t="s">
+      <c r="D68" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -6357,14 +6491,14 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="39"/>
+      <c r="A69" s="38"/>
       <c r="B69" s="12" t="s">
         <v>131</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D69" s="31" t="s">
+      <c r="D69" s="29" t="s">
         <v>317</v>
       </c>
       <c r="E69" s="1" t="s">
@@ -6375,14 +6509,14 @@
       </c>
     </row>
     <row r="70" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="39"/>
+      <c r="A70" s="38"/>
       <c r="B70" s="12" t="s">
         <v>160</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D70" s="31" t="s">
+      <c r="D70" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E70" s="1" t="s">
@@ -6393,14 +6527,14 @@
       </c>
     </row>
     <row r="71" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="39"/>
+      <c r="A71" s="38"/>
       <c r="B71" s="12" t="s">
         <v>141</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="D71" s="31" t="s">
+      <c r="D71" s="29" t="s">
         <v>320</v>
       </c>
       <c r="E71" s="1" t="s">
@@ -6411,14 +6545,14 @@
       </c>
     </row>
     <row r="72" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="39"/>
+      <c r="A72" s="38"/>
       <c r="B72" s="12" t="s">
         <v>142</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="D72" s="31" t="s">
+      <c r="D72" s="29" t="s">
         <v>323</v>
       </c>
       <c r="E72" s="1" t="s">
@@ -6429,14 +6563,14 @@
       </c>
     </row>
     <row r="73" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="39"/>
+      <c r="A73" s="38"/>
       <c r="B73" s="12" t="s">
         <v>143</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="D73" s="31" t="s">
+      <c r="D73" s="29" t="s">
         <v>326</v>
       </c>
       <c r="E73" s="1" t="s">
@@ -6447,14 +6581,14 @@
       </c>
     </row>
     <row r="74" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="39"/>
+      <c r="A74" s="38"/>
       <c r="B74" s="12" t="s">
         <v>138</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D74" s="31" t="s">
+      <c r="D74" s="29" t="s">
         <v>329</v>
       </c>
       <c r="E74" s="1" t="s">
@@ -6465,14 +6599,14 @@
       </c>
     </row>
     <row r="75" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="39"/>
+      <c r="A75" s="38"/>
       <c r="B75" s="12" t="s">
         <v>161</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D75" s="31" t="s">
+      <c r="D75" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E75" s="1" t="s">
@@ -6483,14 +6617,14 @@
       </c>
     </row>
     <row r="76" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="39"/>
+      <c r="A76" s="38"/>
       <c r="B76" s="12" t="s">
         <v>144</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="D76" s="31" t="s">
+      <c r="D76" s="29" t="s">
         <v>333</v>
       </c>
       <c r="E76" s="1" t="s">
@@ -6501,14 +6635,14 @@
       </c>
     </row>
     <row r="77" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="39"/>
+      <c r="A77" s="38"/>
       <c r="B77" s="12" t="s">
         <v>145</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D77" s="31" t="s">
+      <c r="D77" s="29" t="s">
         <v>336</v>
       </c>
       <c r="E77" s="1" t="s">
@@ -6519,14 +6653,14 @@
       </c>
     </row>
     <row r="78" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="39"/>
+      <c r="A78" s="38"/>
       <c r="B78" s="12" t="s">
         <v>146</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="D78" s="31" t="s">
+      <c r="D78" s="29" t="s">
         <v>339</v>
       </c>
       <c r="E78" s="1" t="s">
@@ -6537,14 +6671,14 @@
       </c>
     </row>
     <row r="79" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="39"/>
+      <c r="A79" s="38"/>
       <c r="B79" s="12" t="s">
         <v>147</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D79" s="31" t="s">
+      <c r="D79" s="29" t="s">
         <v>342</v>
       </c>
       <c r="E79" s="1" t="s">
@@ -6555,14 +6689,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="39"/>
+      <c r="A80" s="38"/>
       <c r="B80" s="12" t="s">
         <v>148</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="D80" s="31" t="s">
+      <c r="D80" s="29" t="s">
         <v>345</v>
       </c>
       <c r="E80" s="1" t="s">
@@ -6573,14 +6707,14 @@
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="39"/>
+      <c r="A81" s="38"/>
       <c r="B81" s="12" t="s">
         <v>141</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="D81" s="31" t="s">
+      <c r="D81" s="29" t="s">
         <v>348</v>
       </c>
       <c r="E81" s="1" t="s">
@@ -6591,14 +6725,14 @@
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="39"/>
+      <c r="A82" s="38"/>
       <c r="B82" s="12" t="s">
         <v>138</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D82" s="31" t="s">
+      <c r="D82" s="29" t="s">
         <v>351</v>
       </c>
       <c r="E82" s="1" t="s">
@@ -6609,14 +6743,14 @@
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="39"/>
+      <c r="A83" s="38"/>
       <c r="B83" s="12" t="s">
         <v>162</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D83" s="31" t="s">
+      <c r="D83" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E83" s="1" t="s">
@@ -6627,14 +6761,14 @@
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="39"/>
+      <c r="A84" s="38"/>
       <c r="B84" s="12" t="s">
         <v>149</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D84" s="31" t="s">
+      <c r="D84" s="29" t="s">
         <v>354</v>
       </c>
       <c r="E84" s="1" t="s">
@@ -6645,14 +6779,14 @@
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="39"/>
+      <c r="A85" s="38"/>
       <c r="B85" s="12" t="s">
         <v>150</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="D85" s="31" t="s">
+      <c r="D85" s="29" t="s">
         <v>357</v>
       </c>
       <c r="E85" s="1" t="s">
@@ -6663,14 +6797,14 @@
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="39"/>
+      <c r="A86" s="38"/>
       <c r="B86" s="12" t="s">
         <v>138</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="D86" s="31" t="s">
+      <c r="D86" s="29" t="s">
         <v>359</v>
       </c>
       <c r="E86" s="1" t="s">
@@ -6681,14 +6815,14 @@
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="39"/>
+      <c r="A87" s="38"/>
       <c r="B87" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D87" s="31" t="s">
+      <c r="D87" s="29" t="s">
         <v>35</v>
       </c>
       <c r="E87" s="1" t="s">
@@ -6699,14 +6833,14 @@
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="39"/>
+      <c r="A88" s="38"/>
       <c r="B88" s="12" t="s">
         <v>151</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="D88" s="31" t="s">
+      <c r="D88" s="29" t="s">
         <v>362</v>
       </c>
       <c r="E88" s="1" t="s">
@@ -6717,14 +6851,14 @@
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="39"/>
+      <c r="A89" s="38"/>
       <c r="B89" s="12" t="s">
         <v>152</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="D89" s="31" t="s">
+      <c r="D89" s="29" t="s">
         <v>365</v>
       </c>
       <c r="E89" s="1" t="s">
@@ -6735,14 +6869,14 @@
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="39"/>
+      <c r="A90" s="38"/>
       <c r="B90" s="12" t="s">
         <v>153</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="D90" s="31" t="s">
+      <c r="D90" s="29" t="s">
         <v>368</v>
       </c>
       <c r="E90" s="1" t="s">
@@ -6753,20 +6887,20 @@
       </c>
     </row>
     <row r="91" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="40"/>
-      <c r="B91" s="32" t="s">
+      <c r="A91" s="39"/>
+      <c r="B91" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="C91" s="33" t="s">
+      <c r="C91" s="31" t="s">
         <v>453</v>
       </c>
-      <c r="D91" s="34" t="s">
+      <c r="D91" s="32" t="s">
         <v>371</v>
       </c>
-      <c r="E91" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="F91" s="33" t="s">
+      <c r="E91" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="F91" s="31" t="s">
         <v>454</v>
       </c>
     </row>
@@ -6852,11 +6986,13 @@
       <c r="I101" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="A5:A33"/>
     <mergeCell ref="A34:A62"/>
     <mergeCell ref="A63:A91"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/output/Tables/mmc1.xlsx
+++ b/output/Tables/mmc1.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\luzh29\Library\Projects\WGS_GWAS_and_MR\output\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D8432C-2C63-4990-86F5-5E2B9B7EE633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9A7903-D320-40C2-B0A2-8E0E1B818E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" tabRatio="692" activeTab="1" xr2:uid="{B1B36BAE-942B-7148-AF58-4A36D0B24BEE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="692" activeTab="4" xr2:uid="{B1B36BAE-942B-7148-AF58-4A36D0B24BEE}"/>
   </bookViews>
   <sheets>
     <sheet name="Table S1" sheetId="49" r:id="rId1"/>
     <sheet name="Table S2" sheetId="53" r:id="rId2"/>
     <sheet name="Table S3" sheetId="51" r:id="rId3"/>
     <sheet name="Table S4" sheetId="52" r:id="rId4"/>
+    <sheet name="Table S5" sheetId="54" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="511">
   <si>
     <t>Disease</t>
   </si>
@@ -1724,6 +1725,45 @@
   </si>
   <si>
     <t>Cancer diagnosed by doctor | Instance 0-3; Coding Meaning: https://biobank.ndph.ox.ac.uk/showcase/field.cgi?id=2453</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Principal components</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eigenvalue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>difference</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>twstat</t>
+  </si>
+  <si>
+    <t>NA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table S5. Tracy-Widom statistics of top 30 principal components for the UKBB cohorts, by phenotypes and ethnicities.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>twstat: Tracy-Widom statistic.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect n*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*effect n is the effective number of independent markers/samples.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA: not available.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6999,16 +7039,1903 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC88E03-DBCE-4AE3-86E5-68AC9CDB987B}">
+  <dimension ref="A1:J104"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.875" style="12" customWidth="1"/>
+    <col min="2" max="2" width="27" style="10" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="19.125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="11.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="31.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="22.875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="11" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>501</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="10">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>34.405000000000001</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="E5" s="1">
+        <v>11.81</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1.3508300000000001E-13</v>
+      </c>
+      <c r="G5" s="1">
+        <v>60.408999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="38"/>
+      <c r="B6" s="10">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>15.432</v>
+      </c>
+      <c r="D6" s="1">
+        <v>-18.972999999999999</v>
+      </c>
+      <c r="E6" s="1">
+        <v>13.997</v>
+      </c>
+      <c r="F6" s="1">
+        <v>5.0215200000000001E-17</v>
+      </c>
+      <c r="G6" s="1">
+        <v>301.08499999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="38"/>
+      <c r="B7" s="10">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>12.2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-3.2320000000000002</v>
+      </c>
+      <c r="E7" s="1">
+        <v>20.241</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2.8580900000000001E-28</v>
+      </c>
+      <c r="G7" s="1">
+        <v>732.77499999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="38"/>
+      <c r="B8" s="10">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1">
+        <v>7.6479999999999997</v>
+      </c>
+      <c r="D8" s="1">
+        <v>-4.5519999999999996</v>
+      </c>
+      <c r="E8" s="1">
+        <v>12.257999999999999</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2.82331E-14</v>
+      </c>
+      <c r="G8" s="1">
+        <v>4352.2690000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="38"/>
+      <c r="B9" s="10">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>7.4589999999999996</v>
+      </c>
+      <c r="D9" s="1">
+        <v>-0.189</v>
+      </c>
+      <c r="E9" s="1">
+        <v>19.318999999999999</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1.7529999999999999E-26</v>
+      </c>
+      <c r="G9" s="1">
+        <v>7325.8649999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="38"/>
+      <c r="B10" s="10">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1">
+        <v>6.46</v>
+      </c>
+      <c r="D10" s="1">
+        <v>-0.999</v>
+      </c>
+      <c r="E10" s="1">
+        <v>10.804</v>
+      </c>
+      <c r="F10" s="1">
+        <v>4.0646999999999998E-12</v>
+      </c>
+      <c r="G10" s="1">
+        <v>24673.268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="38"/>
+      <c r="B11" s="10">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1">
+        <v>6.2450000000000001</v>
+      </c>
+      <c r="D11" s="1">
+        <v>-0.215</v>
+      </c>
+      <c r="E11" s="1">
+        <v>8.1549999999999994</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1.5109400000000002E-8</v>
+      </c>
+      <c r="G11" s="1">
+        <v>39833.605000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="38"/>
+      <c r="B12" s="10">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1">
+        <v>6.0789999999999997</v>
+      </c>
+      <c r="D12" s="1">
+        <v>-0.16600000000000001</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3.5979999999999999</v>
+      </c>
+      <c r="F12" s="1">
+        <v>5.1616399999999995E-4</v>
+      </c>
+      <c r="G12" s="1">
+        <v>57874.345999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="38"/>
+      <c r="B13" s="10">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1">
+        <v>6.0289999999999999</v>
+      </c>
+      <c r="D13" s="1">
+        <v>-0.05</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3.3140000000000001</v>
+      </c>
+      <c r="F13" s="1">
+        <v>9.1978000000000003E-4</v>
+      </c>
+      <c r="G13" s="1">
+        <v>71139.604000000007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="38"/>
+      <c r="B14" s="10">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5.9409999999999998</v>
+      </c>
+      <c r="D14" s="1">
+        <v>-8.7999999999999995E-2</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-0.58299999999999996</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.29766799999999999</v>
+      </c>
+      <c r="G14" s="1">
+        <v>87789.077000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="38"/>
+      <c r="B15" s="10">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1">
+        <v>5.915</v>
+      </c>
+      <c r="D15" s="1">
+        <v>-2.5999999999999999E-2</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-1.0289999999999999</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.425182</v>
+      </c>
+      <c r="G15" s="1">
+        <v>96203.793999999994</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="38"/>
+      <c r="B16" s="10">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5.8890000000000002</v>
+      </c>
+      <c r="D16" s="1">
+        <v>-2.5999999999999999E-2</v>
+      </c>
+      <c r="E16" s="1">
+        <v>-1.67</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0.62729999999999997</v>
+      </c>
+      <c r="G16" s="1">
+        <v>104500.33900000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="38"/>
+      <c r="B17" s="10">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1">
+        <v>5.8719999999999999</v>
+      </c>
+      <c r="D17" s="1">
+        <v>-1.7000000000000001E-2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>-1.7110000000000001</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.64012100000000005</v>
+      </c>
+      <c r="G17" s="1">
+        <v>111706.451</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="38"/>
+      <c r="B18" s="10">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1">
+        <v>5.8630000000000004</v>
+      </c>
+      <c r="D18" s="1">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>-1.0289999999999999</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0.42511199999999999</v>
+      </c>
+      <c r="G18" s="1">
+        <v>119533.844</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="38"/>
+      <c r="B19" s="10">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5.8570000000000002</v>
+      </c>
+      <c r="D19" s="1">
+        <v>-6.0000000000000001E-3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0.139735</v>
+      </c>
+      <c r="G19" s="1">
+        <v>131547.61199999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="38"/>
+      <c r="B20" s="10">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1">
+        <v>5.8449999999999998</v>
+      </c>
+      <c r="D20" s="1">
+        <v>-1.2E-2</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1.26</v>
+      </c>
+      <c r="F20" s="1">
+        <v>3.3467700000000003E-2</v>
+      </c>
+      <c r="G20" s="1">
+        <v>153990.29699999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="38"/>
+      <c r="B21" s="10">
+        <v>17</v>
+      </c>
+      <c r="C21" s="1">
+        <v>5.8250000000000002</v>
+      </c>
+      <c r="D21" s="1">
+        <v>-0.02</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2.0430000000000001</v>
+      </c>
+      <c r="F21" s="1">
+        <v>9.6745500000000005E-3</v>
+      </c>
+      <c r="G21" s="1">
+        <v>195526.43400000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="38"/>
+      <c r="B22" s="10">
+        <v>18</v>
+      </c>
+      <c r="C22" s="1">
+        <v>5.7789999999999999</v>
+      </c>
+      <c r="D22" s="1">
+        <v>-4.5999999999999999E-2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>-0.29199999999999998</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0.22701099999999999</v>
+      </c>
+      <c r="G22" s="1">
+        <v>271939.46899999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="38"/>
+      <c r="B23" s="10">
+        <v>19</v>
+      </c>
+      <c r="C23" s="1">
+        <v>5.7670000000000003</v>
+      </c>
+      <c r="D23" s="1">
+        <v>-1.2E-2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0.12518499999999999</v>
+      </c>
+      <c r="G23" s="1">
+        <v>322650.60499999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="38"/>
+      <c r="B24" s="10">
+        <v>20</v>
+      </c>
+      <c r="C24" s="1">
+        <v>5.7480000000000002</v>
+      </c>
+      <c r="D24" s="1">
+        <v>-1.9E-2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>-4.3999999999999997E-2</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0.17624899999999999</v>
+      </c>
+      <c r="G24" s="1">
+        <v>408611.29700000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="38"/>
+      <c r="B25" s="10">
+        <v>21</v>
+      </c>
+      <c r="C25" s="1">
+        <v>5.7309999999999999</v>
+      </c>
+      <c r="D25" s="1">
+        <v>-1.7000000000000001E-2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>-0.43</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0.25907599999999997</v>
+      </c>
+      <c r="G25" s="1">
+        <v>516119.56300000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="38"/>
+      <c r="B26" s="10">
+        <v>22</v>
+      </c>
+      <c r="C26" s="1">
+        <v>5.7140000000000004</v>
+      </c>
+      <c r="D26" s="1">
+        <v>-1.7000000000000001E-2</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="38"/>
+      <c r="B27" s="10">
+        <v>23</v>
+      </c>
+      <c r="C27" s="1">
+        <v>5.7060000000000004</v>
+      </c>
+      <c r="D27" s="1">
+        <v>-8.0000000000000002E-3</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="38"/>
+      <c r="B28" s="10">
+        <v>24</v>
+      </c>
+      <c r="C28" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="D28" s="1">
+        <v>-6.0000000000000001E-3</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="38"/>
+      <c r="B29" s="10">
+        <v>25</v>
+      </c>
+      <c r="C29" s="1">
+        <v>5.6820000000000004</v>
+      </c>
+      <c r="D29" s="1">
+        <v>-1.7999999999999999E-2</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="38"/>
+      <c r="B30" s="10">
+        <v>26</v>
+      </c>
+      <c r="C30" s="1">
+        <v>5.6790000000000003</v>
+      </c>
+      <c r="D30" s="1">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="38"/>
+      <c r="B31" s="10">
+        <v>27</v>
+      </c>
+      <c r="C31" s="1">
+        <v>5.6680000000000001</v>
+      </c>
+      <c r="D31" s="1">
+        <v>-1.0999999999999999E-2</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="38"/>
+      <c r="B32" s="10">
+        <v>28</v>
+      </c>
+      <c r="C32" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+      <c r="D32" s="1">
+        <v>-1.4E-2</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="38"/>
+      <c r="B33" s="10">
+        <v>29</v>
+      </c>
+      <c r="C33" s="1">
+        <v>5.6529999999999996</v>
+      </c>
+      <c r="D33" s="1">
+        <v>-1E-3</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="38"/>
+      <c r="B34" s="10">
+        <v>30</v>
+      </c>
+      <c r="C34" s="1">
+        <v>5.6449999999999996</v>
+      </c>
+      <c r="D34" s="1">
+        <v>-8.0000000000000002E-3</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="38"/>
+      <c r="B36" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="38"/>
+      <c r="B37" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A38" s="38"/>
+      <c r="B38" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="38"/>
+      <c r="B39" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="F39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="38"/>
+      <c r="B40" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="7"/>
+      <c r="F40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="38"/>
+      <c r="B41" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E41" s="7"/>
+      <c r="F41" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="38"/>
+      <c r="B42" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="7"/>
+      <c r="F42" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="38"/>
+      <c r="B43" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="E43" s="7"/>
+      <c r="F43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="38"/>
+      <c r="B44" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E44" s="7"/>
+      <c r="F44" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="38"/>
+      <c r="B45" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E45" s="7"/>
+      <c r="F45" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="38"/>
+      <c r="B46" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E46" s="7"/>
+      <c r="F46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="38"/>
+      <c r="B47" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="7"/>
+      <c r="F47" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="38"/>
+      <c r="B48" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="E48" s="7"/>
+      <c r="F48" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="38"/>
+      <c r="B49" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E49" s="7"/>
+      <c r="F49" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="38"/>
+      <c r="B50" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E50" s="7"/>
+      <c r="F50" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="38"/>
+      <c r="B51" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E51" s="7"/>
+      <c r="F51" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="38"/>
+      <c r="B52" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E52" s="7"/>
+      <c r="F52" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="38"/>
+      <c r="B53" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E53" s="7"/>
+      <c r="F53" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="38"/>
+      <c r="B54" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="E54" s="7"/>
+      <c r="F54" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="38"/>
+      <c r="B55" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="7"/>
+      <c r="F55" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="38"/>
+      <c r="B56" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="E56" s="7"/>
+      <c r="F56" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="38"/>
+      <c r="B57" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="E57" s="7"/>
+      <c r="F57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="38"/>
+      <c r="B58" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="E58" s="7"/>
+      <c r="F58" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="38"/>
+      <c r="B59" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" s="7"/>
+      <c r="F59" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="38"/>
+      <c r="B60" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="38"/>
+      <c r="B61" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="38"/>
+      <c r="B62" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="38"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="38"/>
+      <c r="B64" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D65" s="29" t="s">
+        <v>308</v>
+      </c>
+      <c r="E65" s="29"/>
+      <c r="G65" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="38"/>
+      <c r="B66" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D66" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="29"/>
+      <c r="F66" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="38"/>
+      <c r="B67" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D67" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="E67" s="29"/>
+      <c r="F67" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+      <c r="A68" s="38"/>
+      <c r="B68" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D68" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="29"/>
+      <c r="F68" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="38"/>
+      <c r="B69" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D69" s="29" t="s">
+        <v>314</v>
+      </c>
+      <c r="E69" s="29"/>
+      <c r="F69" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="38"/>
+      <c r="B70" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D70" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="29"/>
+      <c r="F70" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="38"/>
+      <c r="B71" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D71" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="E71" s="29"/>
+      <c r="F71" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="38"/>
+      <c r="B72" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D72" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="29"/>
+      <c r="F72" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="38"/>
+      <c r="B73" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D73" s="29" t="s">
+        <v>320</v>
+      </c>
+      <c r="E73" s="29"/>
+      <c r="F73" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="38"/>
+      <c r="B74" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D74" s="29" t="s">
+        <v>323</v>
+      </c>
+      <c r="E74" s="29"/>
+      <c r="F74" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="38"/>
+      <c r="B75" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D75" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="E75" s="29"/>
+      <c r="F75" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="38"/>
+      <c r="B76" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D76" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="E76" s="29"/>
+      <c r="F76" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="38"/>
+      <c r="B77" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" s="29"/>
+      <c r="F77" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="38"/>
+      <c r="B78" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D78" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="E78" s="29"/>
+      <c r="F78" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="38"/>
+      <c r="B79" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D79" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="E79" s="29"/>
+      <c r="F79" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="38"/>
+      <c r="B80" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D80" s="29" t="s">
+        <v>339</v>
+      </c>
+      <c r="E80" s="29"/>
+      <c r="F80" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="38"/>
+      <c r="B81" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D81" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="E81" s="29"/>
+      <c r="F81" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="38"/>
+      <c r="B82" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D82" s="29" t="s">
+        <v>345</v>
+      </c>
+      <c r="E82" s="29"/>
+      <c r="F82" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="38"/>
+      <c r="B83" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="D83" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="E83" s="29"/>
+      <c r="F83" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="38"/>
+      <c r="B84" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D84" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="E84" s="29"/>
+      <c r="F84" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="38"/>
+      <c r="B85" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D85" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" s="29"/>
+      <c r="F85" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="38"/>
+      <c r="B86" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D86" s="29" t="s">
+        <v>354</v>
+      </c>
+      <c r="E86" s="29"/>
+      <c r="F86" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="38"/>
+      <c r="B87" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D87" s="29" t="s">
+        <v>357</v>
+      </c>
+      <c r="E87" s="29"/>
+      <c r="F87" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="38"/>
+      <c r="B88" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D88" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="E88" s="29"/>
+      <c r="F88" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="38"/>
+      <c r="B89" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D89" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E89" s="29"/>
+      <c r="F89" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="38"/>
+      <c r="B90" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D90" s="29" t="s">
+        <v>362</v>
+      </c>
+      <c r="E90" s="29"/>
+      <c r="F90" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="38"/>
+      <c r="B91" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D91" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="E91" s="29"/>
+      <c r="F91" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="38"/>
+      <c r="D92" s="29"/>
+      <c r="E92" s="29"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="38"/>
+      <c r="B93" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D93" s="29" t="s">
+        <v>368</v>
+      </c>
+      <c r="E93" s="29"/>
+      <c r="F93" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="39"/>
+      <c r="B94" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="C94" s="31" t="s">
+        <v>453</v>
+      </c>
+      <c r="D94" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="E94" s="32"/>
+      <c r="F94" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="G94" s="31" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C96" s="7"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="J96" s="12"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="C97" s="7"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="J97" s="12"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C98" s="7"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="J98" s="12"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C99" s="7"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="J99" s="12"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="C100" s="7"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="J100" s="12"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="C101" s="7"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="J101" s="12"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="C102" s="7"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="J102" s="12"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="C103" s="7"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="J103" s="12"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="12" t="s">
+        <v>510</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="A5:A34"/>
+    <mergeCell ref="A35:A64"/>
+    <mergeCell ref="A65:A94"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064E03803A74B364DAEBC39F6C7EEC88B" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="49ce98d08d805b506bcc40b8f43aa161">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7096755d-09e2-49ab-9780-382f17a74ff2" xmlns:ns3="2496ba1d-a99b-4e00-82bd-3ea232f3a0a7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d262d534f3278ea9c672dc9f1d9c575b" ns2:_="" ns3:_="">
     <xsd:import namespace="7096755d-09e2-49ab-9780-382f17a74ff2"/>
@@ -7251,15 +9178,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9135FDFF-2234-4F0B-B4DA-2AE6D09006AB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EBA38C6-46F4-4280-94E3-1F9DA4BE2039}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7276,4 +9204,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9135FDFF-2234-4F0B-B4DA-2AE6D09006AB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>